--- a/research/traditional_assets/database/data/mauritius/mauritius_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_packaging_container.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09062050871498684</v>
+        <v>0.09052282795191435</v>
       </c>
       <c r="C2">
-        <v>1.87</v>
+        <v>1.852418492033826</v>
       </c>
       <c r="D2">
-        <v>1.814</v>
+        <v>1.815118492033826</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.0187</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0187</v>
       </c>
       <c r="G2">
         <v>0.056</v>
@@ -1451,28 +1451,28 @@
         <v>0.83</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00094061</v>
       </c>
       <c r="N2">
-        <v>0.83</v>
+        <v>0.82905939</v>
       </c>
       <c r="O2">
-        <v>0.1245</v>
+        <v>0.1243589085</v>
       </c>
       <c r="P2">
-        <v>0.7055</v>
+        <v>0.7047004815</v>
       </c>
       <c r="Q2">
-        <v>0.9955000000000002</v>
+        <v>0.9947004815000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09062050871498684</v>
+        <v>0.09100533126455995</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246059</v>
+        <v>0.622268400368605</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>882.4060981703362</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09052282795191435</v>
+        <v>0.09042514718884187</v>
       </c>
       <c r="C3">
-        <v>1.852418492033826</v>
+        <v>1.834838364217898</v>
       </c>
       <c r="D3">
-        <v>1.815118492033826</v>
+        <v>1.816238364217898</v>
       </c>
       <c r="E3">
-        <v>0.0187</v>
+        <v>0.0374</v>
       </c>
       <c r="F3">
-        <v>0.0187</v>
+        <v>0.0374</v>
       </c>
       <c r="G3">
         <v>0.056</v>
@@ -1533,28 +1533,28 @@
         <v>0.83</v>
       </c>
       <c r="M3">
-        <v>0.00094061</v>
+        <v>0.00188122</v>
       </c>
       <c r="N3">
-        <v>0.82905939</v>
+        <v>0.8281187799999999</v>
       </c>
       <c r="O3">
-        <v>0.1243589085</v>
+        <v>0.124217817</v>
       </c>
       <c r="P3">
-        <v>0.7047004815</v>
+        <v>0.7039009629999999</v>
       </c>
       <c r="Q3">
-        <v>0.9947004815000001</v>
+        <v>0.9939009630000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09100533126455995</v>
+        <v>0.09139800733555294</v>
       </c>
       <c r="T3">
-        <v>0.622268400368605</v>
+        <v>0.6276737342910532</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>882.4060981703362</v>
+        <v>441.2030490851681</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09042514718884187</v>
+        <v>0.09032746642576939</v>
       </c>
       <c r="C4">
-        <v>1.834838364217898</v>
+        <v>1.817259619108324</v>
       </c>
       <c r="D4">
-        <v>1.816238364217898</v>
+        <v>1.817359619108324</v>
       </c>
       <c r="E4">
-        <v>0.0374</v>
+        <v>0.0561</v>
       </c>
       <c r="F4">
-        <v>0.0374</v>
+        <v>0.0561</v>
       </c>
       <c r="G4">
         <v>0.056</v>
@@ -1615,28 +1615,28 @@
         <v>0.83</v>
       </c>
       <c r="M4">
-        <v>0.00188122</v>
+        <v>0.00282183</v>
       </c>
       <c r="N4">
-        <v>0.8281187799999999</v>
+        <v>0.8271781699999999</v>
       </c>
       <c r="O4">
-        <v>0.124217817</v>
+        <v>0.1240767255</v>
       </c>
       <c r="P4">
-        <v>0.7039009629999999</v>
+        <v>0.7031014444999999</v>
       </c>
       <c r="Q4">
-        <v>0.9939009630000001</v>
+        <v>0.9931014445</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09139800733555294</v>
+        <v>0.09179877982038082</v>
       </c>
       <c r="T4">
-        <v>0.6276737342910532</v>
+        <v>0.6331905183974692</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>441.2030490851681</v>
+        <v>294.1353660567787</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09032746642576939</v>
+        <v>0.09022978566269692</v>
       </c>
       <c r="C5">
-        <v>1.817259619108324</v>
+        <v>1.799682259267527</v>
       </c>
       <c r="D5">
-        <v>1.817359619108324</v>
+        <v>1.818482259267527</v>
       </c>
       <c r="E5">
-        <v>0.0561</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="F5">
-        <v>0.0561</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="G5">
         <v>0.056</v>
@@ -1697,28 +1697,28 @@
         <v>0.83</v>
       </c>
       <c r="M5">
-        <v>0.00282183</v>
+        <v>0.00376244</v>
       </c>
       <c r="N5">
-        <v>0.8271781699999999</v>
+        <v>0.8262375599999999</v>
       </c>
       <c r="O5">
-        <v>0.1240767255</v>
+        <v>0.123935634</v>
       </c>
       <c r="P5">
-        <v>0.7031014444999999</v>
+        <v>0.702301926</v>
       </c>
       <c r="Q5">
-        <v>0.9931014445</v>
+        <v>0.9923019260000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09179877982038082</v>
+        <v>0.09220790173197596</v>
       </c>
       <c r="T5">
-        <v>0.6331905183974692</v>
+        <v>0.6388222355061024</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>294.1353660567787</v>
+        <v>220.601524542584</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09022978566269692</v>
+        <v>0.09013210489962442</v>
       </c>
       <c r="C6">
-        <v>1.799682259267527</v>
+        <v>1.782106287264267</v>
       </c>
       <c r="D6">
-        <v>1.818482259267527</v>
+        <v>1.819606287264266</v>
       </c>
       <c r="E6">
-        <v>0.07480000000000001</v>
+        <v>0.09350000000000001</v>
       </c>
       <c r="F6">
-        <v>0.07480000000000001</v>
+        <v>0.09350000000000001</v>
       </c>
       <c r="G6">
         <v>0.056</v>
@@ -1779,28 +1779,28 @@
         <v>0.83</v>
       </c>
       <c r="M6">
-        <v>0.00376244</v>
+        <v>0.00470305</v>
       </c>
       <c r="N6">
-        <v>0.8262375599999999</v>
+        <v>0.8252969499999999</v>
       </c>
       <c r="O6">
-        <v>0.123935634</v>
+        <v>0.1237945425</v>
       </c>
       <c r="P6">
-        <v>0.702301926</v>
+        <v>0.7015024074999999</v>
       </c>
       <c r="Q6">
-        <v>0.9923019260000001</v>
+        <v>0.9915024075000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09220790173197596</v>
+        <v>0.09262563673644678</v>
       </c>
       <c r="T6">
-        <v>0.6388222355061024</v>
+        <v>0.6445725150801804</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>220.601524542584</v>
+        <v>176.4812196340672</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09013210489962442</v>
+        <v>0.09003442413655197</v>
       </c>
       <c r="C7">
-        <v>1.782106287264267</v>
+        <v>1.764531705673656</v>
       </c>
       <c r="D7">
-        <v>1.819606287264266</v>
+        <v>1.820731705673656</v>
       </c>
       <c r="E7">
-        <v>0.09350000000000001</v>
+        <v>0.1122</v>
       </c>
       <c r="F7">
-        <v>0.09350000000000001</v>
+        <v>0.1122</v>
       </c>
       <c r="G7">
         <v>0.056</v>
@@ -1861,28 +1861,28 @@
         <v>0.83</v>
       </c>
       <c r="M7">
-        <v>0.00470305</v>
+        <v>0.005643660000000001</v>
       </c>
       <c r="N7">
-        <v>0.8252969499999999</v>
+        <v>0.8243563399999999</v>
       </c>
       <c r="O7">
-        <v>0.1237945425</v>
+        <v>0.123653451</v>
       </c>
       <c r="P7">
-        <v>0.7015024074999999</v>
+        <v>0.7007028889999999</v>
       </c>
       <c r="Q7">
-        <v>0.9915024075000001</v>
+        <v>0.990702889</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09262563673644678</v>
+        <v>0.09305225971973613</v>
       </c>
       <c r="T7">
-        <v>0.6445725150801804</v>
+        <v>0.650445141028175</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>176.4812196340672</v>
+        <v>147.0676830283894</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09003442413655197</v>
+        <v>0.08993674337347948</v>
       </c>
       <c r="C8">
-        <v>1.764531705673656</v>
+        <v>1.746958517077185</v>
       </c>
       <c r="D8">
-        <v>1.820731705673656</v>
+        <v>1.821858517077185</v>
       </c>
       <c r="E8">
-        <v>0.1122</v>
+        <v>0.1309</v>
       </c>
       <c r="F8">
-        <v>0.1122</v>
+        <v>0.1309</v>
       </c>
       <c r="G8">
         <v>0.056</v>
@@ -1943,28 +1943,28 @@
         <v>0.83</v>
       </c>
       <c r="M8">
-        <v>0.00564366</v>
+        <v>0.006584269999999999</v>
       </c>
       <c r="N8">
-        <v>0.8243563399999999</v>
+        <v>0.82341573</v>
       </c>
       <c r="O8">
-        <v>0.123653451</v>
+        <v>0.1235123595</v>
       </c>
       <c r="P8">
-        <v>0.7007028889999999</v>
+        <v>0.6999033705</v>
       </c>
       <c r="Q8">
-        <v>0.990702889</v>
+        <v>0.9899033705000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09305225971973613</v>
+        <v>0.09348805739083814</v>
       </c>
       <c r="T8">
-        <v>0.650445141028175</v>
+        <v>0.6564440600073091</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>147.0676830283894</v>
+        <v>126.0580140243338</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08993674337347947</v>
+        <v>0.08983906261040701</v>
       </c>
       <c r="C9">
-        <v>1.746958517077185</v>
+        <v>1.729386724062736</v>
       </c>
       <c r="D9">
-        <v>1.821858517077185</v>
+        <v>1.822986724062736</v>
       </c>
       <c r="E9">
-        <v>0.1309</v>
+        <v>0.1496</v>
       </c>
       <c r="F9">
-        <v>0.1309</v>
+        <v>0.1496</v>
       </c>
       <c r="G9">
         <v>0.056</v>
@@ -2025,28 +2025,28 @@
         <v>0.83</v>
       </c>
       <c r="M9">
-        <v>0.006584270000000001</v>
+        <v>0.00752488</v>
       </c>
       <c r="N9">
-        <v>0.82341573</v>
+        <v>0.82247512</v>
       </c>
       <c r="O9">
-        <v>0.1235123595</v>
+        <v>0.123371268</v>
       </c>
       <c r="P9">
-        <v>0.6999033705</v>
+        <v>0.699103852</v>
       </c>
       <c r="Q9">
-        <v>0.9899033705000001</v>
+        <v>0.9891038520000002</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09348805739083814</v>
+        <v>0.09393332892435544</v>
       </c>
       <c r="T9">
-        <v>0.6564440600073091</v>
+        <v>0.6625733902685985</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>126.0580140243337</v>
+        <v>110.300762271292</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08983906261040701</v>
+        <v>0.08974138184733452</v>
       </c>
       <c r="C10">
-        <v>1.729386724062736</v>
+        <v>1.711816329224607</v>
       </c>
       <c r="D10">
-        <v>1.822986724062736</v>
+        <v>1.824116329224607</v>
       </c>
       <c r="E10">
-        <v>0.1496</v>
+        <v>0.1683</v>
       </c>
       <c r="F10">
-        <v>0.1496</v>
+        <v>0.1683</v>
       </c>
       <c r="G10">
         <v>0.056</v>
@@ -2107,28 +2107,28 @@
         <v>0.83</v>
       </c>
       <c r="M10">
-        <v>0.00752488</v>
+        <v>0.008465489999999999</v>
       </c>
       <c r="N10">
-        <v>0.82247512</v>
+        <v>0.82153451</v>
       </c>
       <c r="O10">
-        <v>0.123371268</v>
+        <v>0.1232301765</v>
       </c>
       <c r="P10">
-        <v>0.699103852</v>
+        <v>0.6983043335</v>
       </c>
       <c r="Q10">
-        <v>0.9891038520000002</v>
+        <v>0.9883043335000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09393332892435544</v>
+        <v>0.09438838664542254</v>
       </c>
       <c r="T10">
-        <v>0.6625733902685985</v>
+        <v>0.668837431085081</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>110.300762271292</v>
+        <v>98.04512201892626</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08974138184733452</v>
+        <v>0.08964370108426205</v>
       </c>
       <c r="C11">
-        <v>1.711816329224607</v>
+        <v>1.69424733516353</v>
       </c>
       <c r="D11">
-        <v>1.824116329224607</v>
+        <v>1.82524733516353</v>
       </c>
       <c r="E11">
-        <v>0.1683</v>
+        <v>0.187</v>
       </c>
       <c r="F11">
-        <v>0.1683</v>
+        <v>0.187</v>
       </c>
       <c r="G11">
         <v>0.056</v>
@@ -2189,28 +2189,28 @@
         <v>0.83</v>
       </c>
       <c r="M11">
-        <v>0.008465489999999999</v>
+        <v>0.009406099999999999</v>
       </c>
       <c r="N11">
-        <v>0.82153451</v>
+        <v>0.8205939</v>
       </c>
       <c r="O11">
-        <v>0.1232301765</v>
+        <v>0.123089085</v>
       </c>
       <c r="P11">
-        <v>0.6983043335</v>
+        <v>0.6975048150000001</v>
       </c>
       <c r="Q11">
-        <v>0.9883043335000001</v>
+        <v>0.9875048150000002</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09438838664542254</v>
+        <v>0.09485355676029116</v>
       </c>
       <c r="T11">
-        <v>0.668837431085081</v>
+        <v>0.6752406728085966</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>98.04512201892626</v>
+        <v>88.24060981703364</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08964370108426205</v>
+        <v>0.08954602032118955</v>
       </c>
       <c r="C12">
-        <v>1.69424733516353</v>
+        <v>1.67667974448669</v>
       </c>
       <c r="D12">
-        <v>1.82524733516353</v>
+        <v>1.82637974448669</v>
       </c>
       <c r="E12">
-        <v>0.187</v>
+        <v>0.2057</v>
       </c>
       <c r="F12">
-        <v>0.187</v>
+        <v>0.2057</v>
       </c>
       <c r="G12">
         <v>0.056</v>
@@ -2271,28 +2271,28 @@
         <v>0.83</v>
       </c>
       <c r="M12">
-        <v>0.009406100000000001</v>
+        <v>0.01034671</v>
       </c>
       <c r="N12">
-        <v>0.8205939</v>
+        <v>0.81965329</v>
       </c>
       <c r="O12">
-        <v>0.123089085</v>
+        <v>0.1229479935</v>
       </c>
       <c r="P12">
-        <v>0.6975048150000001</v>
+        <v>0.6967052965</v>
       </c>
       <c r="Q12">
-        <v>0.9875048150000002</v>
+        <v>0.9867052965000002</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09485355676029116</v>
+        <v>0.09532918013616803</v>
       </c>
       <c r="T12">
-        <v>0.6752406728085966</v>
+        <v>0.6817878076045505</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>88.24060981703362</v>
+        <v>80.21873619730329</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08954602032118955</v>
+        <v>0.08944833955811707</v>
       </c>
       <c r="C13">
-        <v>1.67667974448669</v>
+        <v>1.659113559807748</v>
       </c>
       <c r="D13">
-        <v>1.82637974448669</v>
+        <v>1.827513559807747</v>
       </c>
       <c r="E13">
-        <v>0.2057</v>
+        <v>0.2244</v>
       </c>
       <c r="F13">
-        <v>0.2057</v>
+        <v>0.2244</v>
       </c>
       <c r="G13">
         <v>0.056</v>
@@ -2353,28 +2353,28 @@
         <v>0.83</v>
       </c>
       <c r="M13">
-        <v>0.01034671</v>
+        <v>0.01128732</v>
       </c>
       <c r="N13">
-        <v>0.81965329</v>
+        <v>0.81871268</v>
       </c>
       <c r="O13">
-        <v>0.1229479935</v>
+        <v>0.122806902</v>
       </c>
       <c r="P13">
-        <v>0.6967052965</v>
+        <v>0.695905778</v>
       </c>
       <c r="Q13">
-        <v>0.9867052965000002</v>
+        <v>0.9859057780000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09532918013616803</v>
+        <v>0.09581561313422395</v>
       </c>
       <c r="T13">
-        <v>0.6817878076045505</v>
+        <v>0.6884837409185943</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>80.21873619730329</v>
+        <v>73.53384151419469</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08944833955811707</v>
+        <v>0.08935065879504459</v>
       </c>
       <c r="C14">
-        <v>1.659113559807748</v>
+        <v>1.641548783746857</v>
       </c>
       <c r="D14">
-        <v>1.827513559807747</v>
+        <v>1.828648783746857</v>
       </c>
       <c r="E14">
-        <v>0.2244</v>
+        <v>0.2431</v>
       </c>
       <c r="F14">
-        <v>0.2244</v>
+        <v>0.2431</v>
       </c>
       <c r="G14">
         <v>0.056</v>
@@ -2435,28 +2435,28 @@
         <v>0.83</v>
       </c>
       <c r="M14">
-        <v>0.01128732</v>
+        <v>0.01222793</v>
       </c>
       <c r="N14">
-        <v>0.81871268</v>
+        <v>0.81777207</v>
       </c>
       <c r="O14">
-        <v>0.122806902</v>
+        <v>0.1226658105</v>
       </c>
       <c r="P14">
-        <v>0.695905778</v>
+        <v>0.6951062594999999</v>
       </c>
       <c r="Q14">
-        <v>0.9859057780000001</v>
+        <v>0.9851062595000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09581561313422395</v>
+        <v>0.09631322850005125</v>
       </c>
       <c r="T14">
-        <v>0.6884837409185943</v>
+        <v>0.6953336037341105</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>73.53384151419469</v>
+        <v>67.87739216694894</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08935065879504459</v>
+        <v>0.0892529780319721</v>
       </c>
       <c r="C15">
-        <v>1.641548783746857</v>
+        <v>1.623985418930686</v>
       </c>
       <c r="D15">
-        <v>1.828648783746857</v>
+        <v>1.829785418930686</v>
       </c>
       <c r="E15">
-        <v>0.2431</v>
+        <v>0.2618</v>
       </c>
       <c r="F15">
-        <v>0.2431</v>
+        <v>0.2618</v>
       </c>
       <c r="G15">
         <v>0.056</v>
@@ -2517,28 +2517,28 @@
         <v>0.83</v>
       </c>
       <c r="M15">
-        <v>0.01222793</v>
+        <v>0.01316854</v>
       </c>
       <c r="N15">
-        <v>0.81777207</v>
+        <v>0.81683146</v>
       </c>
       <c r="O15">
-        <v>0.1226658105</v>
+        <v>0.122524719</v>
       </c>
       <c r="P15">
-        <v>0.6951062594999999</v>
+        <v>0.694306741</v>
       </c>
       <c r="Q15">
-        <v>0.9851062595000001</v>
+        <v>0.9843067410000002</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09631322850005125</v>
+        <v>0.09682241631624663</v>
       </c>
       <c r="T15">
-        <v>0.6953336037341105</v>
+        <v>0.7023427656848711</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>67.87739216694894</v>
+        <v>63.02900701216686</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0892529780319721</v>
+        <v>0.08915529726889963</v>
       </c>
       <c r="C16">
-        <v>1.623985418930686</v>
+        <v>1.606423467992439</v>
       </c>
       <c r="D16">
-        <v>1.829785418930686</v>
+        <v>1.830923467992439</v>
       </c>
       <c r="E16">
-        <v>0.2618</v>
+        <v>0.2805000000000001</v>
       </c>
       <c r="F16">
-        <v>0.2618</v>
+        <v>0.2805000000000001</v>
       </c>
       <c r="G16">
         <v>0.056</v>
@@ -2599,28 +2599,28 @@
         <v>0.83</v>
       </c>
       <c r="M16">
-        <v>0.01316854</v>
+        <v>0.01410915</v>
       </c>
       <c r="N16">
-        <v>0.81683146</v>
+        <v>0.8158908499999999</v>
       </c>
       <c r="O16">
-        <v>0.122524719</v>
+        <v>0.1223836275</v>
       </c>
       <c r="P16">
-        <v>0.694306741</v>
+        <v>0.6935072225</v>
       </c>
       <c r="Q16">
-        <v>0.9843067410000002</v>
+        <v>0.9835072225000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09682241631624663</v>
+        <v>0.09734358502223486</v>
       </c>
       <c r="T16">
-        <v>0.7023427656848711</v>
+        <v>0.7095168490932967</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>63.02900701216686</v>
+        <v>58.82707321135574</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08915529726889963</v>
+        <v>0.08905761650582715</v>
       </c>
       <c r="C17">
-        <v>1.606423467992439</v>
+        <v>1.588862933571875</v>
       </c>
       <c r="D17">
-        <v>1.830923467992439</v>
+        <v>1.832062933571875</v>
       </c>
       <c r="E17">
-        <v>0.2805</v>
+        <v>0.2992</v>
       </c>
       <c r="F17">
-        <v>0.2805</v>
+        <v>0.2992</v>
       </c>
       <c r="G17">
         <v>0.056</v>
@@ -2681,28 +2681,28 @@
         <v>0.83</v>
       </c>
       <c r="M17">
-        <v>0.01410915</v>
+        <v>0.01504976</v>
       </c>
       <c r="N17">
-        <v>0.8158908499999999</v>
+        <v>0.8149502399999999</v>
       </c>
       <c r="O17">
-        <v>0.1223836275</v>
+        <v>0.122242536</v>
       </c>
       <c r="P17">
-        <v>0.6935072225</v>
+        <v>0.6927077039999999</v>
       </c>
       <c r="Q17">
-        <v>0.9835072225000001</v>
+        <v>0.9827077040000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09734358502223486</v>
+        <v>0.09787716250693709</v>
       </c>
       <c r="T17">
-        <v>0.7095168490932967</v>
+        <v>0.716861744011447</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>58.82707321135575</v>
+        <v>55.15038113564601</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08905761650582715</v>
+        <v>0.08895993574275468</v>
       </c>
       <c r="C18">
-        <v>1.588862933571875</v>
+        <v>1.571303818315326</v>
       </c>
       <c r="D18">
-        <v>1.832062933571875</v>
+        <v>1.833203818315326</v>
       </c>
       <c r="E18">
-        <v>0.2992</v>
+        <v>0.3179</v>
       </c>
       <c r="F18">
-        <v>0.2992</v>
+        <v>0.3179</v>
       </c>
       <c r="G18">
         <v>0.056</v>
@@ -2763,28 +2763,28 @@
         <v>0.83</v>
       </c>
       <c r="M18">
-        <v>0.01504976</v>
+        <v>0.01599037</v>
       </c>
       <c r="N18">
-        <v>0.8149502399999999</v>
+        <v>0.8140096299999999</v>
       </c>
       <c r="O18">
-        <v>0.122242536</v>
+        <v>0.1221014445</v>
       </c>
       <c r="P18">
-        <v>0.6927077039999999</v>
+        <v>0.6919081855</v>
       </c>
       <c r="Q18">
-        <v>0.9827077040000001</v>
+        <v>0.9819081855000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09787716250693709</v>
+        <v>0.09842359728042732</v>
       </c>
       <c r="T18">
-        <v>0.716861744011447</v>
+        <v>0.7243836243493114</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>55.15038113564601</v>
+        <v>51.90624106884331</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08895993574275468</v>
+        <v>0.0888622549796822</v>
       </c>
       <c r="C19">
-        <v>1.571303818315326</v>
+        <v>1.553746124875724</v>
       </c>
       <c r="D19">
-        <v>1.833203818315326</v>
+        <v>1.834346124875724</v>
       </c>
       <c r="E19">
-        <v>0.3179</v>
+        <v>0.3366000000000001</v>
       </c>
       <c r="F19">
-        <v>0.3179</v>
+        <v>0.3366000000000001</v>
       </c>
       <c r="G19">
         <v>0.056</v>
@@ -2845,28 +2845,28 @@
         <v>0.83</v>
       </c>
       <c r="M19">
-        <v>0.01599037</v>
+        <v>0.01693098</v>
       </c>
       <c r="N19">
-        <v>0.8140096299999999</v>
+        <v>0.8130690199999999</v>
       </c>
       <c r="O19">
-        <v>0.1221014445</v>
+        <v>0.121960353</v>
       </c>
       <c r="P19">
-        <v>0.6919081855</v>
+        <v>0.691108667</v>
       </c>
       <c r="Q19">
-        <v>0.9819081855000001</v>
+        <v>0.9811086670000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09842359728042732</v>
+        <v>0.09898335973131975</v>
       </c>
       <c r="T19">
-        <v>0.7243836243493114</v>
+        <v>0.7320889651832214</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>51.90624106884331</v>
+        <v>49.02256100946312</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0888622549796822</v>
+        <v>0.08876457421660972</v>
       </c>
       <c r="C20">
-        <v>1.553746124875724</v>
+        <v>1.536189855912613</v>
       </c>
       <c r="D20">
-        <v>1.834346124875724</v>
+        <v>1.835489855912613</v>
       </c>
       <c r="E20">
-        <v>0.3366</v>
+        <v>0.3553</v>
       </c>
       <c r="F20">
-        <v>0.3366</v>
+        <v>0.3553</v>
       </c>
       <c r="G20">
         <v>0.056</v>
@@ -2927,28 +2927,28 @@
         <v>0.83</v>
       </c>
       <c r="M20">
-        <v>0.01693098</v>
+        <v>0.01787159</v>
       </c>
       <c r="N20">
-        <v>0.8130690199999999</v>
+        <v>0.8121284099999999</v>
       </c>
       <c r="O20">
-        <v>0.121960353</v>
+        <v>0.1218192615</v>
       </c>
       <c r="P20">
-        <v>0.691108667</v>
+        <v>0.6903091484999999</v>
       </c>
       <c r="Q20">
-        <v>0.9811086670000001</v>
+        <v>0.9803091485000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09898335973131975</v>
+        <v>0.09955694347729593</v>
       </c>
       <c r="T20">
-        <v>0.7320889651832214</v>
+        <v>0.7399845613463637</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>49.02256100946313</v>
+        <v>46.44242621949138</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08876457421660972</v>
+        <v>0.08866689345353723</v>
       </c>
       <c r="C21">
-        <v>1.536189855912613</v>
+        <v>1.518635014092178</v>
       </c>
       <c r="D21">
-        <v>1.835489855912613</v>
+        <v>1.836635014092179</v>
       </c>
       <c r="E21">
-        <v>0.3553</v>
+        <v>0.3740000000000001</v>
       </c>
       <c r="F21">
-        <v>0.3553</v>
+        <v>0.3740000000000001</v>
       </c>
       <c r="G21">
         <v>0.056</v>
@@ -3009,28 +3009,28 @@
         <v>0.83</v>
       </c>
       <c r="M21">
-        <v>0.01787159</v>
+        <v>0.0188122</v>
       </c>
       <c r="N21">
-        <v>0.8121284099999999</v>
+        <v>0.8111877999999999</v>
       </c>
       <c r="O21">
-        <v>0.1218192615</v>
+        <v>0.12167817</v>
       </c>
       <c r="P21">
-        <v>0.6903091484999999</v>
+        <v>0.6895096299999999</v>
       </c>
       <c r="Q21">
-        <v>0.9803091485000001</v>
+        <v>0.97950963</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09955694347729593</v>
+        <v>0.1001448668169215</v>
       </c>
       <c r="T21">
-        <v>0.7399845613463637</v>
+        <v>0.7480775474135847</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>46.44242621949138</v>
+        <v>44.12030490851681</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08866689345353723</v>
+        <v>0.08856921269046476</v>
       </c>
       <c r="C22">
-        <v>1.518635014092178</v>
+        <v>1.501081602087261</v>
       </c>
       <c r="D22">
-        <v>1.836635014092179</v>
+        <v>1.837781602087261</v>
       </c>
       <c r="E22">
-        <v>0.3740000000000001</v>
+        <v>0.3927</v>
       </c>
       <c r="F22">
-        <v>0.3740000000000001</v>
+        <v>0.3927</v>
       </c>
       <c r="G22">
         <v>0.056</v>
@@ -3091,28 +3091,28 @@
         <v>0.83</v>
       </c>
       <c r="M22">
-        <v>0.0188122</v>
+        <v>0.01975281</v>
       </c>
       <c r="N22">
-        <v>0.8111877999999999</v>
+        <v>0.81024719</v>
       </c>
       <c r="O22">
-        <v>0.12167817</v>
+        <v>0.1215370785</v>
       </c>
       <c r="P22">
-        <v>0.6895096299999999</v>
+        <v>0.6887101115000001</v>
       </c>
       <c r="Q22">
-        <v>0.97950963</v>
+        <v>0.9787101115000002</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1001448668169215</v>
+        <v>0.1007476742917275</v>
       </c>
       <c r="T22">
-        <v>0.7480775474135847</v>
+        <v>0.7563754192040264</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>44.12030490851681</v>
+        <v>42.01933800811125</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08856921269046475</v>
+        <v>0.08847153192739228</v>
       </c>
       <c r="C23">
-        <v>1.501081602087261</v>
+        <v>1.483529622577381</v>
       </c>
       <c r="D23">
-        <v>1.837781602087261</v>
+        <v>1.838929622577381</v>
       </c>
       <c r="E23">
-        <v>0.3927</v>
+        <v>0.4114</v>
       </c>
       <c r="F23">
-        <v>0.3927</v>
+        <v>0.4114</v>
       </c>
       <c r="G23">
         <v>0.056</v>
@@ -3173,28 +3173,28 @@
         <v>0.83</v>
       </c>
       <c r="M23">
-        <v>0.01975281</v>
+        <v>0.02069342</v>
       </c>
       <c r="N23">
-        <v>0.81024719</v>
+        <v>0.80930658</v>
       </c>
       <c r="O23">
-        <v>0.1215370785</v>
+        <v>0.121395987</v>
       </c>
       <c r="P23">
-        <v>0.6887101115000001</v>
+        <v>0.687910593</v>
       </c>
       <c r="Q23">
-        <v>0.9787101115000002</v>
+        <v>0.9779105930000002</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1007476742917275</v>
+        <v>0.1013659383684516</v>
       </c>
       <c r="T23">
-        <v>0.7563754192040263</v>
+        <v>0.7648860569378128</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>42.01933800811126</v>
+        <v>40.10936809865165</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08847153192739228</v>
+        <v>0.08837385116431978</v>
       </c>
       <c r="C24">
-        <v>1.483529622577381</v>
+        <v>1.465979078248757</v>
       </c>
       <c r="D24">
-        <v>1.838929622577381</v>
+        <v>1.840079078248757</v>
       </c>
       <c r="E24">
-        <v>0.4114</v>
+        <v>0.4301</v>
       </c>
       <c r="F24">
-        <v>0.4114</v>
+        <v>0.4301</v>
       </c>
       <c r="G24">
         <v>0.056</v>
@@ -3255,28 +3255,28 @@
         <v>0.83</v>
       </c>
       <c r="M24">
-        <v>0.02069342</v>
+        <v>0.02163403</v>
       </c>
       <c r="N24">
-        <v>0.80930658</v>
+        <v>0.80836597</v>
       </c>
       <c r="O24">
-        <v>0.121395987</v>
+        <v>0.1212548955</v>
       </c>
       <c r="P24">
-        <v>0.687910593</v>
+        <v>0.6871110745</v>
       </c>
       <c r="Q24">
-        <v>0.9779105930000002</v>
+        <v>0.9771110745000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1013659383684516</v>
+        <v>0.1020002612523634</v>
       </c>
       <c r="T24">
-        <v>0.7648860569378128</v>
+        <v>0.773617750197152</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>40.10936809865165</v>
+        <v>38.36548252914505</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08837385116431978</v>
+        <v>0.08827617040124731</v>
       </c>
       <c r="C25">
-        <v>1.465979078248757</v>
+        <v>1.448429971794329</v>
       </c>
       <c r="D25">
-        <v>1.840079078248757</v>
+        <v>1.841229971794329</v>
       </c>
       <c r="E25">
-        <v>0.4301</v>
+        <v>0.4488000000000001</v>
       </c>
       <c r="F25">
-        <v>0.4301</v>
+        <v>0.4488000000000001</v>
       </c>
       <c r="G25">
         <v>0.056</v>
@@ -3337,28 +3337,28 @@
         <v>0.83</v>
       </c>
       <c r="M25">
-        <v>0.02163403</v>
+        <v>0.02257464</v>
       </c>
       <c r="N25">
-        <v>0.80836597</v>
+        <v>0.80742536</v>
       </c>
       <c r="O25">
-        <v>0.1212548955</v>
+        <v>0.121113804</v>
       </c>
       <c r="P25">
-        <v>0.6871110745</v>
+        <v>0.6863115559999999</v>
       </c>
       <c r="Q25">
-        <v>0.9771110745000001</v>
+        <v>0.9763115560000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1020002612523634</v>
+        <v>0.1026512768437465</v>
       </c>
       <c r="T25">
-        <v>0.773617750197152</v>
+        <v>0.7825792248580528</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>38.36548252914505</v>
+        <v>36.76692075709734</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08827617040124731</v>
+        <v>0.08817848963817482</v>
       </c>
       <c r="C26">
-        <v>1.448429971794329</v>
+        <v>1.43088230591378</v>
       </c>
       <c r="D26">
-        <v>1.841229971794329</v>
+        <v>1.84238230591378</v>
       </c>
       <c r="E26">
-        <v>0.4488</v>
+        <v>0.4675</v>
       </c>
       <c r="F26">
-        <v>0.4488</v>
+        <v>0.4675</v>
       </c>
       <c r="G26">
         <v>0.056</v>
@@ -3419,28 +3419,28 @@
         <v>0.83</v>
       </c>
       <c r="M26">
-        <v>0.02257464</v>
+        <v>0.02351525</v>
       </c>
       <c r="N26">
-        <v>0.80742536</v>
+        <v>0.80648475</v>
       </c>
       <c r="O26">
-        <v>0.121113804</v>
+        <v>0.1209727125</v>
       </c>
       <c r="P26">
-        <v>0.6863115559999999</v>
+        <v>0.6855120375</v>
       </c>
       <c r="Q26">
-        <v>0.9763115560000001</v>
+        <v>0.9755120375000002</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1026512768437465</v>
+        <v>0.1033196528508998</v>
       </c>
       <c r="T26">
-        <v>0.7825792248580528</v>
+        <v>0.7917796721765775</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>36.76692075709735</v>
+        <v>35.29624392681345</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08817848963817482</v>
+        <v>0.08808080887510233</v>
       </c>
       <c r="C27">
-        <v>1.43088230591378</v>
+        <v>1.413336083313553</v>
       </c>
       <c r="D27">
-        <v>1.84238230591378</v>
+        <v>1.843536083313553</v>
       </c>
       <c r="E27">
-        <v>0.4675</v>
+        <v>0.4862</v>
       </c>
       <c r="F27">
-        <v>0.4675</v>
+        <v>0.4862</v>
       </c>
       <c r="G27">
         <v>0.056</v>
@@ -3501,28 +3501,28 @@
         <v>0.83</v>
       </c>
       <c r="M27">
-        <v>0.02351525</v>
+        <v>0.02445586</v>
       </c>
       <c r="N27">
-        <v>0.80648475</v>
+        <v>0.80554414</v>
       </c>
       <c r="O27">
-        <v>0.1209727125</v>
+        <v>0.120831621</v>
       </c>
       <c r="P27">
-        <v>0.6855120375</v>
+        <v>0.684712519</v>
       </c>
       <c r="Q27">
-        <v>0.9755120375000002</v>
+        <v>0.9747125190000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1033196528508998</v>
+        <v>0.1040060930744626</v>
       </c>
       <c r="T27">
-        <v>0.7917796721765775</v>
+        <v>0.8012287802334409</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>35.29624392681345</v>
+        <v>33.93869608347447</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08808080887510233</v>
+        <v>0.08798312811202987</v>
       </c>
       <c r="C28">
-        <v>1.413336083313553</v>
+        <v>1.395791306706875</v>
       </c>
       <c r="D28">
-        <v>1.843536083313553</v>
+        <v>1.844691306706876</v>
       </c>
       <c r="E28">
-        <v>0.4862</v>
+        <v>0.5049</v>
       </c>
       <c r="F28">
-        <v>0.4862</v>
+        <v>0.5049</v>
       </c>
       <c r="G28">
         <v>0.056</v>
@@ -3583,28 +3583,28 @@
         <v>0.83</v>
       </c>
       <c r="M28">
-        <v>0.02445586</v>
+        <v>0.02539647</v>
       </c>
       <c r="N28">
-        <v>0.80554414</v>
+        <v>0.80460353</v>
       </c>
       <c r="O28">
-        <v>0.120831621</v>
+        <v>0.1206905295</v>
       </c>
       <c r="P28">
-        <v>0.684712519</v>
+        <v>0.6839130004999999</v>
       </c>
       <c r="Q28">
-        <v>0.9747125190000001</v>
+        <v>0.9739130005000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1040060930744626</v>
+        <v>0.104711339879493</v>
       </c>
       <c r="T28">
-        <v>0.8012287802334409</v>
+        <v>0.8109367679630951</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>33.93869608347447</v>
+        <v>32.68170733964208</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08798312811202987</v>
+        <v>0.0878854473489574</v>
       </c>
       <c r="C29">
-        <v>1.395791306706875</v>
+        <v>1.378247978813781</v>
       </c>
       <c r="D29">
-        <v>1.844691306706876</v>
+        <v>1.845847978813781</v>
       </c>
       <c r="E29">
-        <v>0.5049</v>
+        <v>0.5236000000000001</v>
       </c>
       <c r="F29">
-        <v>0.5049</v>
+        <v>0.5236000000000001</v>
       </c>
       <c r="G29">
         <v>0.056</v>
@@ -3665,28 +3665,28 @@
         <v>0.83</v>
       </c>
       <c r="M29">
-        <v>0.02539647</v>
+        <v>0.02633708</v>
       </c>
       <c r="N29">
-        <v>0.80460353</v>
+        <v>0.8036629199999999</v>
       </c>
       <c r="O29">
-        <v>0.1206905295</v>
+        <v>0.120549438</v>
       </c>
       <c r="P29">
-        <v>0.6839130004999999</v>
+        <v>0.683113482</v>
       </c>
       <c r="Q29">
-        <v>0.9739130005000001</v>
+        <v>0.9731134820000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.104711339879493</v>
+        <v>0.1054361768735519</v>
       </c>
       <c r="T29">
-        <v>0.8109367679630951</v>
+        <v>0.820914422018573</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>32.68170733964208</v>
+        <v>31.51450350608343</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0878854473489574</v>
+        <v>0.08778776658588491</v>
       </c>
       <c r="C30">
-        <v>1.378247978813781</v>
+        <v>1.36070610236113</v>
       </c>
       <c r="D30">
-        <v>1.845847978813781</v>
+        <v>1.84700610236113</v>
       </c>
       <c r="E30">
-        <v>0.5236000000000001</v>
+        <v>0.5423000000000001</v>
       </c>
       <c r="F30">
-        <v>0.5236000000000001</v>
+        <v>0.5423000000000001</v>
       </c>
       <c r="G30">
         <v>0.056</v>
@@ -3747,28 +3747,28 @@
         <v>0.83</v>
       </c>
       <c r="M30">
-        <v>0.02633708</v>
+        <v>0.02727769</v>
       </c>
       <c r="N30">
-        <v>0.8036629199999999</v>
+        <v>0.8027223099999999</v>
       </c>
       <c r="O30">
-        <v>0.120549438</v>
+        <v>0.1204083465</v>
       </c>
       <c r="P30">
-        <v>0.683113482</v>
+        <v>0.6823139635</v>
       </c>
       <c r="Q30">
-        <v>0.9731134820000001</v>
+        <v>0.9723139635000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1054361768735519</v>
+        <v>0.1061814318111055</v>
       </c>
       <c r="T30">
-        <v>0.820914422018573</v>
+        <v>0.8311731367516698</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>31.51450350608343</v>
+        <v>30.42779648863228</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0877877665858849</v>
+        <v>0.08769008582281243</v>
       </c>
       <c r="C31">
-        <v>1.36070610236113</v>
+        <v>1.343165680082628</v>
       </c>
       <c r="D31">
-        <v>1.84700610236113</v>
+        <v>1.848165680082628</v>
       </c>
       <c r="E31">
-        <v>0.5423</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="F31">
-        <v>0.5423</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="G31">
         <v>0.056</v>
@@ -3829,28 +3829,28 @@
         <v>0.83</v>
       </c>
       <c r="M31">
-        <v>0.02727769</v>
+        <v>0.0282183</v>
       </c>
       <c r="N31">
-        <v>0.8027223099999999</v>
+        <v>0.8017816999999999</v>
       </c>
       <c r="O31">
-        <v>0.1204083465</v>
+        <v>0.120267255</v>
       </c>
       <c r="P31">
-        <v>0.6823139635</v>
+        <v>0.6815144449999999</v>
       </c>
       <c r="Q31">
-        <v>0.9723139635000001</v>
+        <v>0.9715144450000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1061814318111055</v>
+        <v>0.1069479797468749</v>
       </c>
       <c r="T31">
-        <v>0.8311731367516698</v>
+        <v>0.8417249576199981</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>30.42779648863228</v>
+        <v>29.41353660567787</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08769008582281243</v>
+        <v>0.08759240505973995</v>
       </c>
       <c r="C32">
-        <v>1.343165680082628</v>
+        <v>1.325626714718853</v>
       </c>
       <c r="D32">
-        <v>1.848165680082628</v>
+        <v>1.849326714718853</v>
       </c>
       <c r="E32">
-        <v>0.5610000000000001</v>
+        <v>0.5797</v>
       </c>
       <c r="F32">
-        <v>0.5610000000000001</v>
+        <v>0.5797</v>
       </c>
       <c r="G32">
         <v>0.056</v>
@@ -3911,28 +3911,28 @@
         <v>0.83</v>
       </c>
       <c r="M32">
-        <v>0.0282183</v>
+        <v>0.02915891</v>
       </c>
       <c r="N32">
-        <v>0.8017816999999999</v>
+        <v>0.8008410899999999</v>
       </c>
       <c r="O32">
-        <v>0.120267255</v>
+        <v>0.1201261635</v>
       </c>
       <c r="P32">
-        <v>0.6815144449999999</v>
+        <v>0.6807149265</v>
       </c>
       <c r="Q32">
-        <v>0.9715144450000001</v>
+        <v>0.9707149265000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1069479797468749</v>
+        <v>0.1077367464633912</v>
       </c>
       <c r="T32">
-        <v>0.8417249576199981</v>
+        <v>0.8525826283685678</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>29.41353660567787</v>
+        <v>28.46471284420439</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08759240505973995</v>
+        <v>0.08749472429666745</v>
       </c>
       <c r="C33">
-        <v>1.325626714718853</v>
+        <v>1.308089209017272</v>
       </c>
       <c r="D33">
-        <v>1.849326714718853</v>
+        <v>1.850489209017272</v>
       </c>
       <c r="E33">
-        <v>0.5797</v>
+        <v>0.5984</v>
       </c>
       <c r="F33">
-        <v>0.5797</v>
+        <v>0.5984</v>
       </c>
       <c r="G33">
         <v>0.056</v>
@@ -3993,28 +3993,28 @@
         <v>0.83</v>
       </c>
       <c r="M33">
-        <v>0.02915891</v>
+        <v>0.03009952</v>
       </c>
       <c r="N33">
-        <v>0.8008410899999999</v>
+        <v>0.7999004799999999</v>
       </c>
       <c r="O33">
-        <v>0.1201261635</v>
+        <v>0.119985072</v>
       </c>
       <c r="P33">
-        <v>0.6807149265</v>
+        <v>0.6799154079999999</v>
       </c>
       <c r="Q33">
-        <v>0.9707149265000001</v>
+        <v>0.9699154080000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1077367464633912</v>
+        <v>0.1085487122009816</v>
       </c>
       <c r="T33">
-        <v>0.8525826283685678</v>
+        <v>0.8637596423744482</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>28.46471284420439</v>
+        <v>27.575190567823</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08749472429666745</v>
+        <v>0.087397043533595</v>
       </c>
       <c r="C34">
-        <v>1.308089209017272</v>
+        <v>1.290553165732264</v>
       </c>
       <c r="D34">
-        <v>1.850489209017272</v>
+        <v>1.851653165732264</v>
       </c>
       <c r="E34">
-        <v>0.5984</v>
+        <v>0.6171000000000001</v>
       </c>
       <c r="F34">
-        <v>0.5984</v>
+        <v>0.6171000000000001</v>
       </c>
       <c r="G34">
         <v>0.056</v>
@@ -4075,28 +4075,28 @@
         <v>0.83</v>
       </c>
       <c r="M34">
-        <v>0.03009952</v>
+        <v>0.03104013</v>
       </c>
       <c r="N34">
-        <v>0.7999004799999999</v>
+        <v>0.7989598699999999</v>
       </c>
       <c r="O34">
-        <v>0.119985072</v>
+        <v>0.1198439805</v>
       </c>
       <c r="P34">
-        <v>0.6799154079999999</v>
+        <v>0.6791158894999999</v>
       </c>
       <c r="Q34">
-        <v>0.9699154080000001</v>
+        <v>0.9691158895</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1085487122009816</v>
+        <v>0.1093849157217836</v>
       </c>
       <c r="T34">
-        <v>0.8637596423744482</v>
+        <v>0.8752702985894596</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>27.575190567823</v>
+        <v>26.73957873243443</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.087397043533595</v>
+        <v>0.0872993627705225</v>
       </c>
       <c r="C35">
-        <v>1.290553165732264</v>
+        <v>1.273018587625146</v>
       </c>
       <c r="D35">
-        <v>1.851653165732264</v>
+        <v>1.852818587625146</v>
       </c>
       <c r="E35">
-        <v>0.6171000000000001</v>
+        <v>0.6358</v>
       </c>
       <c r="F35">
-        <v>0.6171000000000001</v>
+        <v>0.6358</v>
       </c>
       <c r="G35">
         <v>0.056</v>
@@ -4157,28 +4157,28 @@
         <v>0.83</v>
       </c>
       <c r="M35">
-        <v>0.03104013</v>
+        <v>0.03198074</v>
       </c>
       <c r="N35">
-        <v>0.7989598699999999</v>
+        <v>0.79801926</v>
       </c>
       <c r="O35">
-        <v>0.1198439805</v>
+        <v>0.119702889</v>
       </c>
       <c r="P35">
-        <v>0.6791158894999999</v>
+        <v>0.678316371</v>
       </c>
       <c r="Q35">
-        <v>0.9691158895</v>
+        <v>0.9683163710000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1093849157217836</v>
+        <v>0.1102464587432159</v>
       </c>
       <c r="T35">
-        <v>0.8752702985894596</v>
+        <v>0.8871297625685622</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>26.73957873243443</v>
+        <v>25.95312053442165</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0872993627705225</v>
+        <v>0.08720168200745003</v>
       </c>
       <c r="C36">
-        <v>1.273018587625146</v>
+        <v>1.255485477464186</v>
       </c>
       <c r="D36">
-        <v>1.852818587625146</v>
+        <v>1.853985477464186</v>
       </c>
       <c r="E36">
-        <v>0.6358</v>
+        <v>0.6545000000000001</v>
       </c>
       <c r="F36">
-        <v>0.6358</v>
+        <v>0.6545000000000001</v>
       </c>
       <c r="G36">
         <v>0.056</v>
@@ -4239,28 +4239,28 @@
         <v>0.83</v>
       </c>
       <c r="M36">
-        <v>0.03198074</v>
+        <v>0.03292135</v>
       </c>
       <c r="N36">
-        <v>0.79801926</v>
+        <v>0.79707865</v>
       </c>
       <c r="O36">
-        <v>0.119702889</v>
+        <v>0.1195617975</v>
       </c>
       <c r="P36">
-        <v>0.678316371</v>
+        <v>0.6775168525</v>
       </c>
       <c r="Q36">
-        <v>0.9683163710000001</v>
+        <v>0.9675168525000002</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1102464587432159</v>
+        <v>0.1111345107806924</v>
       </c>
       <c r="T36">
-        <v>0.8871297625685622</v>
+        <v>0.8993541331316371</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>25.95312053442165</v>
+        <v>25.21160280486675</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08720168200745003</v>
+        <v>0.08710400124437755</v>
       </c>
       <c r="C37">
-        <v>1.255485477464186</v>
+        <v>1.237953838024636</v>
       </c>
       <c r="D37">
-        <v>1.853985477464186</v>
+        <v>1.855153838024636</v>
       </c>
       <c r="E37">
-        <v>0.6545000000000001</v>
+        <v>0.6732000000000001</v>
       </c>
       <c r="F37">
-        <v>0.6545000000000001</v>
+        <v>0.6732000000000001</v>
       </c>
       <c r="G37">
         <v>0.056</v>
@@ -4321,28 +4321,28 @@
         <v>0.83</v>
       </c>
       <c r="M37">
-        <v>0.03292135</v>
+        <v>0.03386196</v>
       </c>
       <c r="N37">
-        <v>0.79707865</v>
+        <v>0.79613804</v>
       </c>
       <c r="O37">
-        <v>0.1195617975</v>
+        <v>0.119420706</v>
       </c>
       <c r="P37">
-        <v>0.6775168525</v>
+        <v>0.676717334</v>
       </c>
       <c r="Q37">
-        <v>0.9675168525000002</v>
+        <v>0.9667173340000002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1111345107806924</v>
+        <v>0.1120503144443399</v>
       </c>
       <c r="T37">
-        <v>0.8993541331316371</v>
+        <v>0.9119605152748083</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>25.21160280486675</v>
+        <v>24.51128050473156</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08710400124437755</v>
+        <v>0.08700632048130506</v>
       </c>
       <c r="C38">
-        <v>1.237953838024636</v>
+        <v>1.220423672088743</v>
       </c>
       <c r="D38">
-        <v>1.855153838024636</v>
+        <v>1.856323672088743</v>
       </c>
       <c r="E38">
-        <v>0.6732</v>
+        <v>0.6919000000000001</v>
       </c>
       <c r="F38">
-        <v>0.6732</v>
+        <v>0.6919000000000001</v>
       </c>
       <c r="G38">
         <v>0.056</v>
@@ -4403,28 +4403,28 @@
         <v>0.83</v>
       </c>
       <c r="M38">
-        <v>0.03386196</v>
+        <v>0.03480257</v>
       </c>
       <c r="N38">
-        <v>0.79613804</v>
+        <v>0.79519743</v>
       </c>
       <c r="O38">
-        <v>0.119420706</v>
+        <v>0.1192796145</v>
       </c>
       <c r="P38">
-        <v>0.676717334</v>
+        <v>0.6759178155</v>
       </c>
       <c r="Q38">
-        <v>0.9667173340000002</v>
+        <v>0.9659178155000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1120503144443399</v>
+        <v>0.1129951912401668</v>
       </c>
       <c r="T38">
-        <v>0.911960515274808</v>
+        <v>0.9249671000256989</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>24.51128050473157</v>
+        <v>23.84881346406314</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08700632048130506</v>
+        <v>0.08690863971823258</v>
       </c>
       <c r="C39">
-        <v>1.220423672088743</v>
+        <v>1.202894982445779</v>
       </c>
       <c r="D39">
-        <v>1.856323672088743</v>
+        <v>1.857494982445779</v>
       </c>
       <c r="E39">
-        <v>0.6919000000000001</v>
+        <v>0.7106</v>
       </c>
       <c r="F39">
-        <v>0.6919000000000001</v>
+        <v>0.7106</v>
       </c>
       <c r="G39">
         <v>0.056</v>
@@ -4485,28 +4485,28 @@
         <v>0.83</v>
       </c>
       <c r="M39">
-        <v>0.03480257</v>
+        <v>0.03574318</v>
       </c>
       <c r="N39">
-        <v>0.79519743</v>
+        <v>0.79425682</v>
       </c>
       <c r="O39">
-        <v>0.1192796145</v>
+        <v>0.119138523</v>
       </c>
       <c r="P39">
-        <v>0.6759178155</v>
+        <v>0.675118297</v>
       </c>
       <c r="Q39">
-        <v>0.9659178155000001</v>
+        <v>0.9651182970000002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1129951912401668</v>
+        <v>0.1139705479326332</v>
       </c>
       <c r="T39">
-        <v>0.9249671000256989</v>
+        <v>0.9383932520266184</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>23.84881346406314</v>
+        <v>23.22121310974569</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08690863971823258</v>
+        <v>0.0868109589551601</v>
       </c>
       <c r="C40">
-        <v>1.202894982445779</v>
+        <v>1.185367771892059</v>
       </c>
       <c r="D40">
-        <v>1.857494982445779</v>
+        <v>1.858667771892059</v>
       </c>
       <c r="E40">
-        <v>0.7106</v>
+        <v>0.7293000000000001</v>
       </c>
       <c r="F40">
-        <v>0.7106</v>
+        <v>0.7293000000000001</v>
       </c>
       <c r="G40">
         <v>0.056</v>
@@ -4567,28 +4567,28 @@
         <v>0.83</v>
       </c>
       <c r="M40">
-        <v>0.03574318</v>
+        <v>0.03668379</v>
       </c>
       <c r="N40">
-        <v>0.79425682</v>
+        <v>0.79331621</v>
       </c>
       <c r="O40">
-        <v>0.119138523</v>
+        <v>0.1189974315</v>
       </c>
       <c r="P40">
-        <v>0.675118297</v>
+        <v>0.6743187785</v>
       </c>
       <c r="Q40">
-        <v>0.9651182970000002</v>
+        <v>0.9643187785000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1139705479326332</v>
+        <v>0.1149778835330494</v>
       </c>
       <c r="T40">
-        <v>0.9383932520266184</v>
+        <v>0.9522596057324859</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>23.22121310974569</v>
+        <v>22.62579738898298</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0868109589551601</v>
+        <v>0.08671327819208763</v>
       </c>
       <c r="C41">
-        <v>1.185367771892059</v>
+        <v>1.167842043230965</v>
       </c>
       <c r="D41">
-        <v>1.858667771892059</v>
+        <v>1.859842043230965</v>
       </c>
       <c r="E41">
-        <v>0.7293000000000001</v>
+        <v>0.7480000000000001</v>
       </c>
       <c r="F41">
-        <v>0.7293000000000001</v>
+        <v>0.7480000000000001</v>
       </c>
       <c r="G41">
         <v>0.056</v>
@@ -4649,28 +4649,28 @@
         <v>0.83</v>
       </c>
       <c r="M41">
-        <v>0.03668379</v>
+        <v>0.0376244</v>
       </c>
       <c r="N41">
-        <v>0.79331621</v>
+        <v>0.7923756</v>
       </c>
       <c r="O41">
-        <v>0.1189974315</v>
+        <v>0.11885634</v>
       </c>
       <c r="P41">
-        <v>0.6743187785</v>
+        <v>0.67351926</v>
       </c>
       <c r="Q41">
-        <v>0.9643187785000001</v>
+        <v>0.9635192600000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1149778835330494</v>
+        <v>0.1160187969868127</v>
       </c>
       <c r="T41">
-        <v>0.9522596057324859</v>
+        <v>0.9665881712285495</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>22.62579738898298</v>
+        <v>22.0601524542584</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08671327819208763</v>
+        <v>0.08661559742901515</v>
       </c>
       <c r="C42">
-        <v>1.167842043230965</v>
+        <v>1.15031779927297</v>
       </c>
       <c r="D42">
-        <v>1.859842043230965</v>
+        <v>1.86101779927297</v>
       </c>
       <c r="E42">
-        <v>0.7480000000000001</v>
+        <v>0.7667</v>
       </c>
       <c r="F42">
-        <v>0.7480000000000001</v>
+        <v>0.7667</v>
       </c>
       <c r="G42">
         <v>0.056</v>
@@ -4731,28 +4731,28 @@
         <v>0.83</v>
       </c>
       <c r="M42">
-        <v>0.0376244</v>
+        <v>0.03856501</v>
       </c>
       <c r="N42">
-        <v>0.7923756</v>
+        <v>0.7914349899999999</v>
       </c>
       <c r="O42">
-        <v>0.11885634</v>
+        <v>0.1187152485</v>
       </c>
       <c r="P42">
-        <v>0.67351926</v>
+        <v>0.6727197414999999</v>
       </c>
       <c r="Q42">
-        <v>0.9635192600000001</v>
+        <v>0.9627197415000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1160187969868127</v>
+        <v>0.1170949956423986</v>
       </c>
       <c r="T42">
-        <v>0.9665881712285495</v>
+        <v>0.9814024508092248</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>22.0601524542584</v>
+        <v>21.52209995537405</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08661559742901515</v>
+        <v>0.08651791666594266</v>
       </c>
       <c r="C43">
-        <v>1.15031779927297</v>
+        <v>1.132795042835656</v>
       </c>
       <c r="D43">
-        <v>1.86101779927297</v>
+        <v>1.862195042835656</v>
       </c>
       <c r="E43">
-        <v>0.7667</v>
+        <v>0.7854000000000001</v>
       </c>
       <c r="F43">
-        <v>0.7667</v>
+        <v>0.7854000000000001</v>
       </c>
       <c r="G43">
         <v>0.056</v>
@@ -4813,28 +4813,28 @@
         <v>0.83</v>
       </c>
       <c r="M43">
-        <v>0.03856501</v>
+        <v>0.03950562000000001</v>
       </c>
       <c r="N43">
-        <v>0.7914349899999999</v>
+        <v>0.7904943799999999</v>
       </c>
       <c r="O43">
-        <v>0.1187152485</v>
+        <v>0.118574157</v>
       </c>
       <c r="P43">
-        <v>0.6727197414999999</v>
+        <v>0.671920223</v>
       </c>
       <c r="Q43">
-        <v>0.9627197415000001</v>
+        <v>0.9619202230000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1170949956423986</v>
+        <v>0.1182083045964529</v>
       </c>
       <c r="T43">
-        <v>0.9814024508092248</v>
+        <v>0.9967275676168202</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>21.52209995537405</v>
+        <v>21.00966900405562</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08651791666594266</v>
+        <v>0.08642023590287019</v>
       </c>
       <c r="C44">
-        <v>1.132795042835656</v>
+        <v>1.115273776743738</v>
       </c>
       <c r="D44">
-        <v>1.862195042835656</v>
+        <v>1.863373776743738</v>
       </c>
       <c r="E44">
-        <v>0.7854</v>
+        <v>0.8041</v>
       </c>
       <c r="F44">
-        <v>0.7854</v>
+        <v>0.8041</v>
       </c>
       <c r="G44">
         <v>0.056</v>
@@ -4895,28 +4895,28 @@
         <v>0.83</v>
       </c>
       <c r="M44">
-        <v>0.03950562</v>
+        <v>0.04044623</v>
       </c>
       <c r="N44">
-        <v>0.7904943799999999</v>
+        <v>0.7895537699999999</v>
       </c>
       <c r="O44">
-        <v>0.118574157</v>
+        <v>0.1184330655</v>
       </c>
       <c r="P44">
-        <v>0.671920223</v>
+        <v>0.6711207044999999</v>
       </c>
       <c r="Q44">
-        <v>0.9619202230000001</v>
+        <v>0.9611207045000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1182083045964529</v>
+        <v>0.1193606770225793</v>
       </c>
       <c r="T44">
-        <v>0.9967275676168201</v>
+        <v>1.012590407821173</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>21.00966900405562</v>
+        <v>20.52107205047293</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08642023590287019</v>
+        <v>0.0863225551397977</v>
       </c>
       <c r="C45">
-        <v>1.115273776743738</v>
+        <v>1.097754003829091</v>
       </c>
       <c r="D45">
-        <v>1.863373776743738</v>
+        <v>1.864554003829092</v>
       </c>
       <c r="E45">
-        <v>0.8041</v>
+        <v>0.8228000000000001</v>
       </c>
       <c r="F45">
-        <v>0.8041</v>
+        <v>0.8228000000000001</v>
       </c>
       <c r="G45">
         <v>0.056</v>
@@ -4977,28 +4977,28 @@
         <v>0.83</v>
       </c>
       <c r="M45">
-        <v>0.04044623</v>
+        <v>0.04138684</v>
       </c>
       <c r="N45">
-        <v>0.7895537699999999</v>
+        <v>0.7886131599999999</v>
       </c>
       <c r="O45">
-        <v>0.1184330655</v>
+        <v>0.118291974</v>
       </c>
       <c r="P45">
-        <v>0.6711207044999999</v>
+        <v>0.6703211859999999</v>
       </c>
       <c r="Q45">
-        <v>0.9611207045000001</v>
+        <v>0.960321186</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1193606770225793</v>
+        <v>0.1205542056067816</v>
       </c>
       <c r="T45">
-        <v>1.012590407821173</v>
+        <v>1.029019778032825</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>20.52107205047293</v>
+        <v>20.05468404932582</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0863225551397977</v>
+        <v>0.08622487437672523</v>
       </c>
       <c r="C46">
-        <v>1.097754003829091</v>
+        <v>1.080235726930767</v>
       </c>
       <c r="D46">
-        <v>1.864554003829092</v>
+        <v>1.865735726930767</v>
       </c>
       <c r="E46">
-        <v>0.8228000000000001</v>
+        <v>0.8415</v>
       </c>
       <c r="F46">
-        <v>0.8228000000000001</v>
+        <v>0.8415</v>
       </c>
       <c r="G46">
         <v>0.056</v>
@@ -5059,28 +5059,28 @@
         <v>0.83</v>
       </c>
       <c r="M46">
-        <v>0.04138684</v>
+        <v>0.04232745</v>
       </c>
       <c r="N46">
-        <v>0.7886131599999999</v>
+        <v>0.7876725499999999</v>
       </c>
       <c r="O46">
-        <v>0.118291974</v>
+        <v>0.1181508825</v>
       </c>
       <c r="P46">
-        <v>0.6703211859999999</v>
+        <v>0.6695216675</v>
       </c>
       <c r="Q46">
-        <v>0.960321186</v>
+        <v>0.9595216675000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1205542056067816</v>
+        <v>0.1217911352304095</v>
       </c>
       <c r="T46">
-        <v>1.029019778032825</v>
+        <v>1.046046579888536</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>20.05468404932582</v>
+        <v>19.60902440378525</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08622487437672523</v>
+        <v>0.08612719361365274</v>
       </c>
       <c r="C47">
-        <v>1.080235726930767</v>
+        <v>1.062718948895019</v>
       </c>
       <c r="D47">
-        <v>1.865735726930767</v>
+        <v>1.866918948895019</v>
       </c>
       <c r="E47">
-        <v>0.8415</v>
+        <v>0.8602000000000001</v>
       </c>
       <c r="F47">
-        <v>0.8415</v>
+        <v>0.8602000000000001</v>
       </c>
       <c r="G47">
         <v>0.056</v>
@@ -5141,28 +5141,28 @@
         <v>0.83</v>
       </c>
       <c r="M47">
-        <v>0.04232745</v>
+        <v>0.04326806</v>
       </c>
       <c r="N47">
-        <v>0.7876725499999999</v>
+        <v>0.7867319399999999</v>
       </c>
       <c r="O47">
-        <v>0.1181508825</v>
+        <v>0.118009791</v>
       </c>
       <c r="P47">
-        <v>0.6695216675</v>
+        <v>0.6687221489999999</v>
       </c>
       <c r="Q47">
-        <v>0.9595216675000001</v>
+        <v>0.9587221490000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1217911352304095</v>
+        <v>0.1230738770623199</v>
       </c>
       <c r="T47">
-        <v>1.046046579888536</v>
+        <v>1.0637040040352</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>19.60902440378525</v>
+        <v>19.18274126457252</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08612719361365274</v>
+        <v>0.08602951285058028</v>
       </c>
       <c r="C48">
-        <v>1.062718948895019</v>
+        <v>1.045203672575327</v>
       </c>
       <c r="D48">
-        <v>1.866918948895019</v>
+        <v>1.868103672575327</v>
       </c>
       <c r="E48">
-        <v>0.8602000000000001</v>
+        <v>0.8789000000000001</v>
       </c>
       <c r="F48">
-        <v>0.8602000000000001</v>
+        <v>0.8789000000000001</v>
       </c>
       <c r="G48">
         <v>0.056</v>
@@ -5223,28 +5223,28 @@
         <v>0.83</v>
       </c>
       <c r="M48">
-        <v>0.04326806</v>
+        <v>0.04420867000000001</v>
       </c>
       <c r="N48">
-        <v>0.7867319399999999</v>
+        <v>0.7857913299999999</v>
       </c>
       <c r="O48">
-        <v>0.118009791</v>
+        <v>0.1178686995</v>
       </c>
       <c r="P48">
-        <v>0.6687221489999999</v>
+        <v>0.6679226304999999</v>
       </c>
       <c r="Q48">
-        <v>0.9587221490000001</v>
+        <v>0.9579226305</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1230738770623199</v>
+        <v>0.1244050242463779</v>
       </c>
       <c r="T48">
-        <v>1.0637040040352</v>
+        <v>1.082027746074191</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>19.18274126457252</v>
+        <v>18.77459783341141</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08602951285058028</v>
+        <v>0.08593183208750778</v>
       </c>
       <c r="C49">
-        <v>1.045203672575327</v>
+        <v>1.027689900832417</v>
       </c>
       <c r="D49">
-        <v>1.868103672575327</v>
+        <v>1.869289900832417</v>
       </c>
       <c r="E49">
-        <v>0.8789000000000001</v>
+        <v>0.8976000000000002</v>
       </c>
       <c r="F49">
-        <v>0.8789000000000001</v>
+        <v>0.8976000000000002</v>
       </c>
       <c r="G49">
         <v>0.056</v>
@@ -5305,28 +5305,28 @@
         <v>0.83</v>
       </c>
       <c r="M49">
-        <v>0.04420867000000001</v>
+        <v>0.04514928000000001</v>
       </c>
       <c r="N49">
-        <v>0.7857913299999999</v>
+        <v>0.78485072</v>
       </c>
       <c r="O49">
-        <v>0.1178686995</v>
+        <v>0.117727608</v>
       </c>
       <c r="P49">
-        <v>0.6679226304999999</v>
+        <v>0.667123112</v>
       </c>
       <c r="Q49">
-        <v>0.9579226305</v>
+        <v>0.9571231120000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1244050242463779</v>
+        <v>0.1257873693990534</v>
       </c>
       <c r="T49">
-        <v>1.082027746074191</v>
+        <v>1.101056247422374</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>18.77459783341141</v>
+        <v>18.38346037854867</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08593183208750778</v>
+        <v>0.0858341513244353</v>
       </c>
       <c r="C50">
-        <v>1.027689900832417</v>
+        <v>1.010177636534288</v>
       </c>
       <c r="D50">
-        <v>1.869289900832417</v>
+        <v>1.870477636534287</v>
       </c>
       <c r="E50">
-        <v>0.8976000000000001</v>
+        <v>0.9163</v>
       </c>
       <c r="F50">
-        <v>0.8976000000000001</v>
+        <v>0.9163</v>
       </c>
       <c r="G50">
         <v>0.056</v>
@@ -5387,28 +5387,28 @@
         <v>0.83</v>
       </c>
       <c r="M50">
-        <v>0.04514928</v>
+        <v>0.04608988999999999</v>
       </c>
       <c r="N50">
-        <v>0.78485072</v>
+        <v>0.78391011</v>
       </c>
       <c r="O50">
-        <v>0.117727608</v>
+        <v>0.1175865165</v>
       </c>
       <c r="P50">
-        <v>0.667123112</v>
+        <v>0.6663235935</v>
       </c>
       <c r="Q50">
-        <v>0.9571231120000001</v>
+        <v>0.9563235935000002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1257873693990534</v>
+        <v>0.1272239241655594</v>
       </c>
       <c r="T50">
-        <v>1.101056247422374</v>
+        <v>1.120830964509701</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>18.38346037854867</v>
+        <v>18.00828771776197</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0858341513244353</v>
+        <v>0.08573647056136281</v>
       </c>
       <c r="C51">
-        <v>1.010177636534288</v>
+        <v>0.9926668825562284</v>
       </c>
       <c r="D51">
-        <v>1.870477636534287</v>
+        <v>1.871666882556228</v>
       </c>
       <c r="E51">
-        <v>0.9163</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F51">
-        <v>0.9163</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="G51">
         <v>0.056</v>
@@ -5469,28 +5469,28 @@
         <v>0.83</v>
       </c>
       <c r="M51">
-        <v>0.04608988999999999</v>
+        <v>0.0470305</v>
       </c>
       <c r="N51">
-        <v>0.78391011</v>
+        <v>0.7829695</v>
       </c>
       <c r="O51">
-        <v>0.1175865165</v>
+        <v>0.117445425</v>
       </c>
       <c r="P51">
-        <v>0.6663235935</v>
+        <v>0.665524075</v>
       </c>
       <c r="Q51">
-        <v>0.9563235935000002</v>
+        <v>0.9555240750000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1272239241655594</v>
+        <v>0.1287179411227256</v>
       </c>
       <c r="T51">
-        <v>1.120830964509701</v>
+        <v>1.141396670280521</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>18.00828771776197</v>
+        <v>17.64812196340672</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08573647056136281</v>
+        <v>0.08563878979829033</v>
       </c>
       <c r="C52">
-        <v>0.9926668825562284</v>
+        <v>0.9751576417808497</v>
       </c>
       <c r="D52">
-        <v>1.871666882556228</v>
+        <v>1.87285764178085</v>
       </c>
       <c r="E52">
-        <v>0.9350000000000001</v>
+        <v>0.9537000000000001</v>
       </c>
       <c r="F52">
-        <v>0.9350000000000001</v>
+        <v>0.9537000000000001</v>
       </c>
       <c r="G52">
         <v>0.056</v>
@@ -5551,28 +5551,28 @@
         <v>0.83</v>
       </c>
       <c r="M52">
-        <v>0.0470305</v>
+        <v>0.04797111</v>
       </c>
       <c r="N52">
-        <v>0.7829695</v>
+        <v>0.78202889</v>
       </c>
       <c r="O52">
-        <v>0.117445425</v>
+        <v>0.1173043335</v>
       </c>
       <c r="P52">
-        <v>0.665524075</v>
+        <v>0.6647245565</v>
       </c>
       <c r="Q52">
-        <v>0.9555240750000001</v>
+        <v>0.9547245565000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1287179411227256</v>
+        <v>0.1302729383638578</v>
       </c>
       <c r="T52">
-        <v>1.141396670280521</v>
+        <v>1.162801792613416</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>17.64812196340672</v>
+        <v>17.3020803562811</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08563878979829033</v>
+        <v>0.08554110903521786</v>
       </c>
       <c r="C53">
-        <v>0.9751576417808497</v>
+        <v>0.9576499170980984</v>
       </c>
       <c r="D53">
-        <v>1.87285764178085</v>
+        <v>1.874049917098098</v>
       </c>
       <c r="E53">
-        <v>0.9537000000000001</v>
+        <v>0.9724</v>
       </c>
       <c r="F53">
-        <v>0.9537000000000001</v>
+        <v>0.9724</v>
       </c>
       <c r="G53">
         <v>0.056</v>
@@ -5633,28 +5633,28 @@
         <v>0.83</v>
       </c>
       <c r="M53">
-        <v>0.04797111</v>
+        <v>0.04891172</v>
       </c>
       <c r="N53">
-        <v>0.78202889</v>
+        <v>0.78108828</v>
       </c>
       <c r="O53">
-        <v>0.1173043335</v>
+        <v>0.117163242</v>
       </c>
       <c r="P53">
-        <v>0.6647245565</v>
+        <v>0.663925038</v>
       </c>
       <c r="Q53">
-        <v>0.9547245565000001</v>
+        <v>0.9539250380000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1302729383638578</v>
+        <v>0.1318927271567039</v>
       </c>
       <c r="T53">
-        <v>1.162801792613416</v>
+        <v>1.185098795043514</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>17.3020803562811</v>
+        <v>16.96934804173723</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08554110903521786</v>
+        <v>0.08544342827214538</v>
       </c>
       <c r="C54">
-        <v>0.9576499170980984</v>
+        <v>0.9401437114052884</v>
       </c>
       <c r="D54">
-        <v>1.874049917098098</v>
+        <v>1.875243711405288</v>
       </c>
       <c r="E54">
-        <v>0.9724</v>
+        <v>0.9911000000000001</v>
       </c>
       <c r="F54">
-        <v>0.9724</v>
+        <v>0.9911000000000001</v>
       </c>
       <c r="G54">
         <v>0.056</v>
@@ -5715,28 +5715,28 @@
         <v>0.83</v>
       </c>
       <c r="M54">
-        <v>0.04891172</v>
+        <v>0.04985233</v>
       </c>
       <c r="N54">
-        <v>0.78108828</v>
+        <v>0.78014767</v>
       </c>
       <c r="O54">
-        <v>0.117163242</v>
+        <v>0.1170221505</v>
       </c>
       <c r="P54">
-        <v>0.663925038</v>
+        <v>0.6631255195</v>
       </c>
       <c r="Q54">
-        <v>0.9539250380000002</v>
+        <v>0.9531255195000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1318927271567039</v>
+        <v>0.1335814431322242</v>
       </c>
       <c r="T54">
-        <v>1.185098795043514</v>
+        <v>1.208344606087659</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>16.96934804173723</v>
+        <v>16.64917166359125</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08544342827214538</v>
+        <v>0.08534574750907289</v>
       </c>
       <c r="C55">
-        <v>0.9401437114052884</v>
+        <v>0.922639027607119</v>
       </c>
       <c r="D55">
-        <v>1.875243711405288</v>
+        <v>1.876439027607119</v>
       </c>
       <c r="E55">
-        <v>0.9911000000000001</v>
+        <v>1.0098</v>
       </c>
       <c r="F55">
-        <v>0.9911000000000001</v>
+        <v>1.0098</v>
       </c>
       <c r="G55">
         <v>0.056</v>
@@ -5797,28 +5797,28 @@
         <v>0.83</v>
       </c>
       <c r="M55">
-        <v>0.04985233</v>
+        <v>0.05079294</v>
       </c>
       <c r="N55">
-        <v>0.78014767</v>
+        <v>0.77920706</v>
       </c>
       <c r="O55">
-        <v>0.1170221505</v>
+        <v>0.116881059</v>
       </c>
       <c r="P55">
-        <v>0.6631255195</v>
+        <v>0.6623260009999999</v>
       </c>
       <c r="Q55">
-        <v>0.9531255195000001</v>
+        <v>0.9523260010000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1335814431322242</v>
+        <v>0.1353435815414628</v>
       </c>
       <c r="T55">
-        <v>1.208344606087659</v>
+        <v>1.232601104568506</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>16.64917166359125</v>
+        <v>16.34085366982104</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08534574750907289</v>
+        <v>0.08524806674600041</v>
       </c>
       <c r="C56">
-        <v>0.922639027607119</v>
+        <v>0.9051358686157005</v>
       </c>
       <c r="D56">
-        <v>1.876439027607119</v>
+        <v>1.877635868615701</v>
       </c>
       <c r="E56">
-        <v>1.0098</v>
+        <v>1.0285</v>
       </c>
       <c r="F56">
-        <v>1.0098</v>
+        <v>1.0285</v>
       </c>
       <c r="G56">
         <v>0.056</v>
@@ -5879,28 +5879,28 @@
         <v>0.83</v>
       </c>
       <c r="M56">
-        <v>0.05079294</v>
+        <v>0.05173355000000001</v>
       </c>
       <c r="N56">
-        <v>0.77920706</v>
+        <v>0.7782664499999999</v>
       </c>
       <c r="O56">
-        <v>0.116881059</v>
+        <v>0.1167399675</v>
       </c>
       <c r="P56">
-        <v>0.6623260009999999</v>
+        <v>0.6615264825</v>
       </c>
       <c r="Q56">
-        <v>0.9523260010000001</v>
+        <v>0.9515264825000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1353435815414628</v>
+        <v>0.1371840372133343</v>
       </c>
       <c r="T56">
-        <v>1.232601104568506</v>
+        <v>1.257935669648502</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>16.34085366982104</v>
+        <v>16.04374723946066</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08524806674600041</v>
+        <v>0.08515038598292794</v>
       </c>
       <c r="C57">
-        <v>0.9051358686157005</v>
+        <v>0.8876342373505779</v>
       </c>
       <c r="D57">
-        <v>1.877635868615701</v>
+        <v>1.878834237350578</v>
       </c>
       <c r="E57">
-        <v>1.0285</v>
+        <v>1.0472</v>
       </c>
       <c r="F57">
-        <v>1.0285</v>
+        <v>1.0472</v>
       </c>
       <c r="G57">
         <v>0.056</v>
@@ -5961,28 +5961,28 @@
         <v>0.83</v>
       </c>
       <c r="M57">
-        <v>0.05173355000000001</v>
+        <v>0.05267416</v>
       </c>
       <c r="N57">
-        <v>0.7782664499999999</v>
+        <v>0.7773258399999999</v>
       </c>
       <c r="O57">
-        <v>0.1167399675</v>
+        <v>0.116598876</v>
       </c>
       <c r="P57">
-        <v>0.6615264825</v>
+        <v>0.660726964</v>
       </c>
       <c r="Q57">
-        <v>0.9515264825000002</v>
+        <v>0.9507269640000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1371840372133343</v>
+        <v>0.1391081499611999</v>
       </c>
       <c r="T57">
-        <v>1.257935669648502</v>
+        <v>1.284421805868498</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>16.04374723946066</v>
+        <v>15.75725175304172</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08515038598292794</v>
+        <v>0.08505270521985547</v>
       </c>
       <c r="C58">
-        <v>0.8876342373505779</v>
+        <v>0.8701341367387543</v>
       </c>
       <c r="D58">
-        <v>1.878834237350578</v>
+        <v>1.880034136738754</v>
       </c>
       <c r="E58">
-        <v>1.0472</v>
+        <v>1.0659</v>
       </c>
       <c r="F58">
-        <v>1.0472</v>
+        <v>1.0659</v>
       </c>
       <c r="G58">
         <v>0.056</v>
@@ -6043,28 +6043,28 @@
         <v>0.83</v>
       </c>
       <c r="M58">
-        <v>0.05267416</v>
+        <v>0.05361477</v>
       </c>
       <c r="N58">
-        <v>0.7773258399999999</v>
+        <v>0.7763852299999999</v>
       </c>
       <c r="O58">
-        <v>0.116598876</v>
+        <v>0.1164577845</v>
       </c>
       <c r="P58">
-        <v>0.660726964</v>
+        <v>0.6599274454999999</v>
       </c>
       <c r="Q58">
-        <v>0.9507269640000001</v>
+        <v>0.9499274455000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1391081499611999</v>
+        <v>0.1411217563252453</v>
       </c>
       <c r="T58">
-        <v>1.284421805868498</v>
+        <v>1.312139855401052</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>15.75725175304172</v>
+        <v>15.48080873983046</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08505270521985547</v>
+        <v>0.08495502445678298</v>
       </c>
       <c r="C59">
-        <v>0.8701341367387543</v>
+        <v>0.8526355697147148</v>
       </c>
       <c r="D59">
-        <v>1.880034136738754</v>
+        <v>1.881235569714715</v>
       </c>
       <c r="E59">
-        <v>1.0659</v>
+        <v>1.0846</v>
       </c>
       <c r="F59">
-        <v>1.0659</v>
+        <v>1.0846</v>
       </c>
       <c r="G59">
         <v>0.056</v>
@@ -6125,28 +6125,28 @@
         <v>0.83</v>
       </c>
       <c r="M59">
-        <v>0.05361477</v>
+        <v>0.05455538000000001</v>
       </c>
       <c r="N59">
-        <v>0.7763852299999999</v>
+        <v>0.7754446199999999</v>
       </c>
       <c r="O59">
-        <v>0.1164577845</v>
+        <v>0.116316693</v>
       </c>
       <c r="P59">
-        <v>0.6599274454999999</v>
+        <v>0.6591279269999999</v>
       </c>
       <c r="Q59">
-        <v>0.9499274455000001</v>
+        <v>0.949127927</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1411217563252453</v>
+        <v>0.1432312487066262</v>
       </c>
       <c r="T59">
-        <v>1.312139855401052</v>
+        <v>1.341177812054203</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>15.48080873983046</v>
+        <v>15.21389824431614</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08495502445678299</v>
+        <v>0.08485734369371051</v>
       </c>
       <c r="C60">
-        <v>0.8526355697147145</v>
+        <v>0.8351385392204502</v>
       </c>
       <c r="D60">
-        <v>1.881235569714715</v>
+        <v>1.88243853922045</v>
       </c>
       <c r="E60">
-        <v>1.0846</v>
+        <v>1.1033</v>
       </c>
       <c r="F60">
-        <v>1.0846</v>
+        <v>1.1033</v>
       </c>
       <c r="G60">
         <v>0.056</v>
@@ -6207,28 +6207,28 @@
         <v>0.83</v>
       </c>
       <c r="M60">
-        <v>0.05455538</v>
+        <v>0.05549599</v>
       </c>
       <c r="N60">
-        <v>0.7754446199999999</v>
+        <v>0.77450401</v>
       </c>
       <c r="O60">
-        <v>0.116316693</v>
+        <v>0.1161756015</v>
       </c>
       <c r="P60">
-        <v>0.6591279269999999</v>
+        <v>0.6583284085000001</v>
       </c>
       <c r="Q60">
-        <v>0.949127927</v>
+        <v>0.9483284085000002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1432312487066262</v>
+        <v>0.1454436431553915</v>
       </c>
       <c r="T60">
-        <v>1.341177812054203</v>
+        <v>1.371632254397752</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>15.21389824431614</v>
+        <v>14.95603556220909</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08485734369371051</v>
+        <v>0.08475966293063801</v>
       </c>
       <c r="C61">
-        <v>0.8351385392204502</v>
+        <v>0.8176430482054813</v>
       </c>
       <c r="D61">
-        <v>1.88243853922045</v>
+        <v>1.883643048205481</v>
       </c>
       <c r="E61">
-        <v>1.1033</v>
+        <v>1.122</v>
       </c>
       <c r="F61">
-        <v>1.1033</v>
+        <v>1.122</v>
       </c>
       <c r="G61">
         <v>0.056</v>
@@ -6289,28 +6289,28 @@
         <v>0.83</v>
       </c>
       <c r="M61">
-        <v>0.05549599</v>
+        <v>0.0564366</v>
       </c>
       <c r="N61">
-        <v>0.77450401</v>
+        <v>0.7735634</v>
       </c>
       <c r="O61">
-        <v>0.1161756015</v>
+        <v>0.11603451</v>
       </c>
       <c r="P61">
-        <v>0.6583284085000001</v>
+        <v>0.65752889</v>
       </c>
       <c r="Q61">
-        <v>0.9483284085000002</v>
+        <v>0.9475288900000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1454436431553915</v>
+        <v>0.147766657326595</v>
       </c>
       <c r="T61">
-        <v>1.371632254397752</v>
+        <v>1.403609418858478</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>14.95603556220909</v>
+        <v>14.70676830283894</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08475966293063801</v>
+        <v>0.08466198216756554</v>
       </c>
       <c r="C62">
-        <v>0.8176430482054813</v>
+        <v>0.800149099626883</v>
       </c>
       <c r="D62">
-        <v>1.883643048205481</v>
+        <v>1.884849099626883</v>
       </c>
       <c r="E62">
-        <v>1.122</v>
+        <v>1.1407</v>
       </c>
       <c r="F62">
-        <v>1.122</v>
+        <v>1.1407</v>
       </c>
       <c r="G62">
         <v>0.056</v>
@@ -6371,28 +6371,28 @@
         <v>0.83</v>
       </c>
       <c r="M62">
-        <v>0.0564366</v>
+        <v>0.05737721</v>
       </c>
       <c r="N62">
-        <v>0.7735634</v>
+        <v>0.77262279</v>
       </c>
       <c r="O62">
-        <v>0.11603451</v>
+        <v>0.1158934185</v>
       </c>
       <c r="P62">
-        <v>0.65752889</v>
+        <v>0.6567293715</v>
       </c>
       <c r="Q62">
-        <v>0.9475288900000002</v>
+        <v>0.9467293715000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.147766657326595</v>
+        <v>0.1502088004296552</v>
       </c>
       <c r="T62">
-        <v>1.403609418858478</v>
+        <v>1.437226437906934</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>14.70676830283894</v>
+        <v>14.46567374049732</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08466198216756554</v>
+        <v>0.08456430140449306</v>
       </c>
       <c r="C63">
-        <v>0.800149099626883</v>
+        <v>0.7826566964493087</v>
       </c>
       <c r="D63">
-        <v>1.884849099626883</v>
+        <v>1.886056696449309</v>
       </c>
       <c r="E63">
-        <v>1.1407</v>
+        <v>1.1594</v>
       </c>
       <c r="F63">
-        <v>1.1407</v>
+        <v>1.1594</v>
       </c>
       <c r="G63">
         <v>0.056</v>
@@ -6453,28 +6453,28 @@
         <v>0.83</v>
       </c>
       <c r="M63">
-        <v>0.05737721</v>
+        <v>0.05831782</v>
       </c>
       <c r="N63">
-        <v>0.77262279</v>
+        <v>0.77168218</v>
       </c>
       <c r="O63">
-        <v>0.1158934185</v>
+        <v>0.115752327</v>
       </c>
       <c r="P63">
-        <v>0.6567293715</v>
+        <v>0.655929853</v>
       </c>
       <c r="Q63">
-        <v>0.9467293715000001</v>
+        <v>0.9459298530000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1502088004296552</v>
+        <v>0.1527794773802449</v>
       </c>
       <c r="T63">
-        <v>1.437226437906934</v>
+        <v>1.472612773747415</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>14.46567374049732</v>
+        <v>14.2323564221022</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08456430140449306</v>
+        <v>0.08446662064142058</v>
       </c>
       <c r="C64">
-        <v>0.7826566964493087</v>
+        <v>0.7651658416450138</v>
       </c>
       <c r="D64">
-        <v>1.886056696449309</v>
+        <v>1.887265841645014</v>
       </c>
       <c r="E64">
-        <v>1.1594</v>
+        <v>1.1781</v>
       </c>
       <c r="F64">
-        <v>1.1594</v>
+        <v>1.1781</v>
       </c>
       <c r="G64">
         <v>0.056</v>
@@ -6535,28 +6535,28 @@
         <v>0.83</v>
       </c>
       <c r="M64">
-        <v>0.05831782</v>
+        <v>0.05925843000000001</v>
       </c>
       <c r="N64">
-        <v>0.77168218</v>
+        <v>0.77074157</v>
       </c>
       <c r="O64">
-        <v>0.115752327</v>
+        <v>0.1156112355</v>
       </c>
       <c r="P64">
-        <v>0.655929853</v>
+        <v>0.6551303345</v>
       </c>
       <c r="Q64">
-        <v>0.9459298530000001</v>
+        <v>0.9451303345000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1527794773802449</v>
+        <v>0.1554891098416772</v>
       </c>
       <c r="T64">
-        <v>1.472612773747415</v>
+        <v>1.509911884498191</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>14.2323564221022</v>
+        <v>14.00644600270375</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08446662064142058</v>
+        <v>0.08436893987834809</v>
       </c>
       <c r="C65">
-        <v>0.7651658416450138</v>
+        <v>0.7476765381938808</v>
       </c>
       <c r="D65">
-        <v>1.887265841645014</v>
+        <v>1.888476538193881</v>
       </c>
       <c r="E65">
-        <v>1.1781</v>
+        <v>1.1968</v>
       </c>
       <c r="F65">
-        <v>1.1781</v>
+        <v>1.1968</v>
       </c>
       <c r="G65">
         <v>0.056</v>
@@ -6617,28 +6617,28 @@
         <v>0.83</v>
       </c>
       <c r="M65">
-        <v>0.05925843000000001</v>
+        <v>0.06019904</v>
       </c>
       <c r="N65">
-        <v>0.77074157</v>
+        <v>0.76980096</v>
       </c>
       <c r="O65">
-        <v>0.1156112355</v>
+        <v>0.115470144</v>
       </c>
       <c r="P65">
-        <v>0.6551303345</v>
+        <v>0.654330816</v>
       </c>
       <c r="Q65">
-        <v>0.9451303345000002</v>
+        <v>0.9443308160000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1554891098416772</v>
+        <v>0.1583492774398558</v>
       </c>
       <c r="T65">
-        <v>1.509911884498191</v>
+        <v>1.549283168068455</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>14.00644600270375</v>
+        <v>13.7875952839115</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08436893987834809</v>
+        <v>0.08427125911527561</v>
       </c>
       <c r="C66">
-        <v>0.7476765381938808</v>
+        <v>0.730188789083444</v>
       </c>
       <c r="D66">
-        <v>1.888476538193881</v>
+        <v>1.889688789083444</v>
       </c>
       <c r="E66">
-        <v>1.1968</v>
+        <v>1.2155</v>
       </c>
       <c r="F66">
-        <v>1.1968</v>
+        <v>1.2155</v>
       </c>
       <c r="G66">
         <v>0.056</v>
@@ -6699,28 +6699,28 @@
         <v>0.83</v>
       </c>
       <c r="M66">
-        <v>0.06019904</v>
+        <v>0.06113965</v>
       </c>
       <c r="N66">
-        <v>0.76980096</v>
+        <v>0.76886035</v>
       </c>
       <c r="O66">
-        <v>0.115470144</v>
+        <v>0.1153290525</v>
       </c>
       <c r="P66">
-        <v>0.654330816</v>
+        <v>0.6535312974999999</v>
       </c>
       <c r="Q66">
-        <v>0.9443308160000001</v>
+        <v>0.9435312975000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1583492774398558</v>
+        <v>0.1613728831865018</v>
       </c>
       <c r="T66">
-        <v>1.549283168068455</v>
+        <v>1.590904239271305</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>13.7875952839115</v>
+        <v>13.57547843338979</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08427125911527561</v>
+        <v>0.08417357835220314</v>
       </c>
       <c r="C67">
-        <v>0.730188789083444</v>
+        <v>0.7127025973089129</v>
       </c>
       <c r="D67">
-        <v>1.889688789083444</v>
+        <v>1.890902597308913</v>
       </c>
       <c r="E67">
-        <v>1.2155</v>
+        <v>1.2342</v>
       </c>
       <c r="F67">
-        <v>1.2155</v>
+        <v>1.2342</v>
       </c>
       <c r="G67">
         <v>0.056</v>
@@ -6781,28 +6781,28 @@
         <v>0.83</v>
       </c>
       <c r="M67">
-        <v>0.06113965</v>
+        <v>0.06208026000000001</v>
       </c>
       <c r="N67">
-        <v>0.76886035</v>
+        <v>0.76791974</v>
       </c>
       <c r="O67">
-        <v>0.1153290525</v>
+        <v>0.115187961</v>
       </c>
       <c r="P67">
-        <v>0.6535312974999999</v>
+        <v>0.652731779</v>
       </c>
       <c r="Q67">
-        <v>0.9435312975000001</v>
+        <v>0.9427317790000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1613728831865018</v>
+        <v>0.1645743480947151</v>
       </c>
       <c r="T67">
-        <v>1.590904239271305</v>
+        <v>1.634973608780206</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>13.57547843338979</v>
+        <v>13.36978936621721</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08417357835220314</v>
+        <v>0.08407589758913064</v>
       </c>
       <c r="C68">
-        <v>0.7127025973089129</v>
+        <v>0.6952179658731987</v>
       </c>
       <c r="D68">
-        <v>1.890902597308913</v>
+        <v>1.892117965873199</v>
       </c>
       <c r="E68">
-        <v>1.2342</v>
+        <v>1.2529</v>
       </c>
       <c r="F68">
-        <v>1.2342</v>
+        <v>1.2529</v>
       </c>
       <c r="G68">
         <v>0.056</v>
@@ -6863,28 +6863,28 @@
         <v>0.83</v>
       </c>
       <c r="M68">
-        <v>0.06208026000000001</v>
+        <v>0.06302087000000001</v>
       </c>
       <c r="N68">
-        <v>0.76791974</v>
+        <v>0.76697913</v>
       </c>
       <c r="O68">
-        <v>0.115187961</v>
+        <v>0.1150468695</v>
       </c>
       <c r="P68">
-        <v>0.652731779</v>
+        <v>0.6519322605</v>
       </c>
       <c r="Q68">
-        <v>0.9427317790000002</v>
+        <v>0.9419322605000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1645743480947151</v>
+        <v>0.1679698411791838</v>
       </c>
       <c r="T68">
-        <v>1.634973608780206</v>
+        <v>1.681713849168434</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>13.36978936621721</v>
+        <v>13.17024027119905</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08407589758913064</v>
+        <v>0.08397821682605819</v>
       </c>
       <c r="C69">
-        <v>0.6952179658731987</v>
+        <v>0.6777348977869362</v>
       </c>
       <c r="D69">
-        <v>1.892117965873199</v>
+        <v>1.893334897786936</v>
       </c>
       <c r="E69">
-        <v>1.2529</v>
+        <v>1.2716</v>
       </c>
       <c r="F69">
-        <v>1.2529</v>
+        <v>1.2716</v>
       </c>
       <c r="G69">
         <v>0.056</v>
@@ -6945,28 +6945,28 @@
         <v>0.83</v>
       </c>
       <c r="M69">
-        <v>0.06302087000000001</v>
+        <v>0.06396148</v>
       </c>
       <c r="N69">
-        <v>0.76697913</v>
+        <v>0.7660385199999999</v>
       </c>
       <c r="O69">
-        <v>0.1150468695</v>
+        <v>0.114905778</v>
       </c>
       <c r="P69">
-        <v>0.6519322605</v>
+        <v>0.6511327419999999</v>
       </c>
       <c r="Q69">
-        <v>0.9419322605000001</v>
+        <v>0.9411327420000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1679698411791838</v>
+        <v>0.1715775525814318</v>
       </c>
       <c r="T69">
-        <v>1.681713849168434</v>
+        <v>1.731375354580926</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>13.17024027119905</v>
+        <v>12.97656026721083</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08397821682605819</v>
+        <v>0.0847602860629857</v>
       </c>
       <c r="C70">
-        <v>0.6777348977869362</v>
+        <v>0.6493353594274061</v>
       </c>
       <c r="D70">
-        <v>1.893334897786936</v>
+        <v>1.883635359427406</v>
       </c>
       <c r="E70">
-        <v>1.2716</v>
+        <v>1.2903</v>
       </c>
       <c r="F70">
-        <v>1.2716</v>
+        <v>1.2903</v>
       </c>
       <c r="G70">
         <v>0.056</v>
@@ -7027,45 +7027,45 @@
         <v>0.83</v>
       </c>
       <c r="M70">
-        <v>0.06396148</v>
+        <v>0.06683754000000001</v>
       </c>
       <c r="N70">
-        <v>0.7660385199999999</v>
+        <v>0.76316246</v>
       </c>
       <c r="O70">
-        <v>0.114905778</v>
+        <v>0.114474369</v>
       </c>
       <c r="P70">
-        <v>0.6511327419999999</v>
+        <v>0.648688091</v>
       </c>
       <c r="Q70">
-        <v>0.9411327420000001</v>
+        <v>0.9386880910000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1715775525814318</v>
+        <v>0.1754180195580184</v>
       </c>
       <c r="T70">
-        <v>1.731375354580926</v>
+        <v>1.784240828084546</v>
       </c>
       <c r="U70">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V70">
         <v>0.15</v>
       </c>
       <c r="W70">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y70">
-        <v>12.97656026721083</v>
+        <v>12.41817098594592</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0847602860629857</v>
+        <v>0.08467535529991321</v>
       </c>
       <c r="C71">
-        <v>0.6493353594274061</v>
+        <v>0.631683892097886</v>
       </c>
       <c r="D71">
-        <v>1.883635359427406</v>
+        <v>1.884683892097886</v>
       </c>
       <c r="E71">
-        <v>1.2903</v>
+        <v>1.309</v>
       </c>
       <c r="F71">
-        <v>1.2903</v>
+        <v>1.309</v>
       </c>
       <c r="G71">
         <v>0.056</v>
@@ -7109,28 +7109,28 @@
         <v>0.83</v>
       </c>
       <c r="M71">
-        <v>0.06683754000000001</v>
+        <v>0.06780620000000001</v>
       </c>
       <c r="N71">
-        <v>0.76316246</v>
+        <v>0.7621937999999999</v>
       </c>
       <c r="O71">
-        <v>0.114474369</v>
+        <v>0.11432907</v>
       </c>
       <c r="P71">
-        <v>0.648688091</v>
+        <v>0.64786473</v>
       </c>
       <c r="Q71">
-        <v>0.9386880910000002</v>
+        <v>0.9378647300000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1754180195580184</v>
+        <v>0.1795145176663774</v>
       </c>
       <c r="T71">
-        <v>1.784240828084546</v>
+        <v>1.840630666488408</v>
       </c>
       <c r="U71">
         <v>0.0518</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>12.41817098594592</v>
+        <v>12.24076854328955</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08467535529991321</v>
+        <v>0.08459042453684074</v>
       </c>
       <c r="C72">
-        <v>0.631683892097886</v>
+        <v>0.6140335927577996</v>
       </c>
       <c r="D72">
-        <v>1.884683892097886</v>
+        <v>1.8857335927578</v>
       </c>
       <c r="E72">
-        <v>1.309</v>
+        <v>1.3277</v>
       </c>
       <c r="F72">
-        <v>1.309</v>
+        <v>1.3277</v>
       </c>
       <c r="G72">
         <v>0.056</v>
@@ -7191,28 +7191,28 @@
         <v>0.83</v>
       </c>
       <c r="M72">
-        <v>0.06780620000000001</v>
+        <v>0.06877486000000002</v>
       </c>
       <c r="N72">
-        <v>0.7621937999999999</v>
+        <v>0.76122514</v>
       </c>
       <c r="O72">
-        <v>0.11432907</v>
+        <v>0.114183771</v>
       </c>
       <c r="P72">
-        <v>0.64786473</v>
+        <v>0.647041369</v>
       </c>
       <c r="Q72">
-        <v>0.9378647300000001</v>
+        <v>0.9370413690000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1795145176663774</v>
+        <v>0.1838935328856578</v>
       </c>
       <c r="T72">
-        <v>1.840630666488408</v>
+        <v>1.90090945926495</v>
       </c>
       <c r="U72">
         <v>0.0518</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>12.24076854328955</v>
+        <v>12.06836335253899</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08459042453684074</v>
+        <v>0.08450549377376826</v>
       </c>
       <c r="C73">
-        <v>0.6140335927577998</v>
+        <v>0.5963844633598185</v>
       </c>
       <c r="D73">
-        <v>1.8857335927578</v>
+        <v>1.886784463359819</v>
       </c>
       <c r="E73">
-        <v>1.3277</v>
+        <v>1.3464</v>
       </c>
       <c r="F73">
-        <v>1.3277</v>
+        <v>1.3464</v>
       </c>
       <c r="G73">
         <v>0.056</v>
@@ -7273,28 +7273,28 @@
         <v>0.83</v>
       </c>
       <c r="M73">
-        <v>0.06877486000000001</v>
+        <v>0.06974352</v>
       </c>
       <c r="N73">
-        <v>0.76122514</v>
+        <v>0.76025648</v>
       </c>
       <c r="O73">
-        <v>0.114183771</v>
+        <v>0.114038472</v>
       </c>
       <c r="P73">
-        <v>0.647041369</v>
+        <v>0.646218008</v>
       </c>
       <c r="Q73">
-        <v>0.9370413690000001</v>
+        <v>0.9362180080000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1838935328856577</v>
+        <v>0.1885853349063152</v>
       </c>
       <c r="T73">
-        <v>1.90090945926495</v>
+        <v>1.965493880096959</v>
       </c>
       <c r="U73">
         <v>0.0518</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>12.06836335253899</v>
+        <v>11.90074719486484</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08450549377376826</v>
+        <v>0.08442056301069578</v>
       </c>
       <c r="C74">
-        <v>0.5963844633598185</v>
+        <v>0.5787365058609684</v>
       </c>
       <c r="D74">
-        <v>1.886784463359819</v>
+        <v>1.887836505860968</v>
       </c>
       <c r="E74">
-        <v>1.3464</v>
+        <v>1.3651</v>
       </c>
       <c r="F74">
-        <v>1.3464</v>
+        <v>1.3651</v>
       </c>
       <c r="G74">
         <v>0.056</v>
@@ -7355,28 +7355,28 @@
         <v>0.83</v>
       </c>
       <c r="M74">
-        <v>0.06974352</v>
+        <v>0.07071218</v>
       </c>
       <c r="N74">
-        <v>0.76025648</v>
+        <v>0.7592878199999999</v>
       </c>
       <c r="O74">
-        <v>0.114038472</v>
+        <v>0.113893173</v>
       </c>
       <c r="P74">
-        <v>0.646218008</v>
+        <v>0.6453946469999999</v>
       </c>
       <c r="Q74">
-        <v>0.9362180080000001</v>
+        <v>0.9353946470000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1885853349063152</v>
+        <v>0.1936246778173918</v>
       </c>
       <c r="T74">
-        <v>1.965493880096959</v>
+        <v>2.034862332101709</v>
       </c>
       <c r="U74">
         <v>0.0518</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>11.90074719486484</v>
+        <v>11.73772326068861</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08442056301069578</v>
+        <v>0.0843356322476233</v>
       </c>
       <c r="C75">
-        <v>0.5787365058609684</v>
+        <v>0.5610897222226421</v>
       </c>
       <c r="D75">
-        <v>1.887836505860968</v>
+        <v>1.888889722222642</v>
       </c>
       <c r="E75">
-        <v>1.3651</v>
+        <v>1.3838</v>
       </c>
       <c r="F75">
-        <v>1.3651</v>
+        <v>1.3838</v>
       </c>
       <c r="G75">
         <v>0.056</v>
@@ -7437,28 +7437,28 @@
         <v>0.83</v>
       </c>
       <c r="M75">
-        <v>0.07071218</v>
+        <v>0.07168084000000001</v>
       </c>
       <c r="N75">
-        <v>0.7592878199999999</v>
+        <v>0.75831916</v>
       </c>
       <c r="O75">
-        <v>0.113893173</v>
+        <v>0.113747874</v>
       </c>
       <c r="P75">
-        <v>0.6453946469999999</v>
+        <v>0.644571286</v>
       </c>
       <c r="Q75">
-        <v>0.9353946470000001</v>
+        <v>0.9345712860000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1936246778173918</v>
+        <v>0.1990516624908588</v>
       </c>
       <c r="T75">
-        <v>2.034862332101709</v>
+        <v>2.109566818876056</v>
       </c>
       <c r="U75">
         <v>0.0518</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>11.73772326068861</v>
+        <v>11.57910537878741</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0843356322476233</v>
+        <v>0.08425070148455081</v>
       </c>
       <c r="C76">
-        <v>0.5610897222226421</v>
+        <v>0.5434441144106137</v>
       </c>
       <c r="D76">
-        <v>1.888889722222642</v>
+        <v>1.889944114410614</v>
       </c>
       <c r="E76">
-        <v>1.3838</v>
+        <v>1.4025</v>
       </c>
       <c r="F76">
-        <v>1.3838</v>
+        <v>1.4025</v>
       </c>
       <c r="G76">
         <v>0.056</v>
@@ -7519,28 +7519,28 @@
         <v>0.83</v>
       </c>
       <c r="M76">
-        <v>0.07168084000000001</v>
+        <v>0.07264950000000001</v>
       </c>
       <c r="N76">
-        <v>0.75831916</v>
+        <v>0.7573504999999999</v>
       </c>
       <c r="O76">
-        <v>0.113747874</v>
+        <v>0.113602575</v>
       </c>
       <c r="P76">
-        <v>0.644571286</v>
+        <v>0.643747925</v>
       </c>
       <c r="Q76">
-        <v>0.9345712860000002</v>
+        <v>0.9337479250000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1990516624908588</v>
+        <v>0.2049128059382033</v>
       </c>
       <c r="T76">
-        <v>2.109566818876056</v>
+        <v>2.190247664592351</v>
       </c>
       <c r="U76">
         <v>0.0518</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>11.57910537878741</v>
+        <v>11.42471730707025</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08425070148455081</v>
+        <v>0.08416577072147835</v>
       </c>
       <c r="C77">
-        <v>0.5434441144106137</v>
+        <v>0.5257996843950468</v>
       </c>
       <c r="D77">
-        <v>1.889944114410614</v>
+        <v>1.890999684395047</v>
       </c>
       <c r="E77">
-        <v>1.4025</v>
+        <v>1.4212</v>
       </c>
       <c r="F77">
-        <v>1.4025</v>
+        <v>1.4212</v>
       </c>
       <c r="G77">
         <v>0.056</v>
@@ -7601,28 +7601,28 @@
         <v>0.83</v>
       </c>
       <c r="M77">
-        <v>0.07264950000000001</v>
+        <v>0.07361816</v>
       </c>
       <c r="N77">
-        <v>0.7573504999999999</v>
+        <v>0.75638184</v>
       </c>
       <c r="O77">
-        <v>0.113602575</v>
+        <v>0.113457276</v>
       </c>
       <c r="P77">
-        <v>0.643747925</v>
+        <v>0.642924564</v>
       </c>
       <c r="Q77">
-        <v>0.9337479250000001</v>
+        <v>0.9329245640000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2049128059382033</v>
+        <v>0.2112623780061598</v>
       </c>
       <c r="T77">
-        <v>2.190247664592351</v>
+        <v>2.277651914118337</v>
       </c>
       <c r="U77">
         <v>0.0518</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>11.42471730707025</v>
+        <v>11.27439207934564</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08416577072147835</v>
+        <v>0.08408083995840586</v>
       </c>
       <c r="C78">
-        <v>0.5257996843950468</v>
+        <v>0.5081564341505105</v>
       </c>
       <c r="D78">
-        <v>1.890999684395047</v>
+        <v>1.892056434150511</v>
       </c>
       <c r="E78">
-        <v>1.4212</v>
+        <v>1.4399</v>
       </c>
       <c r="F78">
-        <v>1.4212</v>
+        <v>1.4399</v>
       </c>
       <c r="G78">
         <v>0.056</v>
@@ -7683,28 +7683,28 @@
         <v>0.83</v>
       </c>
       <c r="M78">
-        <v>0.07361816</v>
+        <v>0.07458682000000001</v>
       </c>
       <c r="N78">
-        <v>0.75638184</v>
+        <v>0.7554131799999999</v>
       </c>
       <c r="O78">
-        <v>0.113457276</v>
+        <v>0.113311977</v>
       </c>
       <c r="P78">
-        <v>0.642924564</v>
+        <v>0.642101203</v>
       </c>
       <c r="Q78">
-        <v>0.9329245640000001</v>
+        <v>0.9321012030000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2112623780061598</v>
+        <v>0.2181640867756777</v>
       </c>
       <c r="T78">
-        <v>2.277651914118337</v>
+        <v>2.372656533168322</v>
       </c>
       <c r="U78">
         <v>0.0518</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>11.27439207934564</v>
+        <v>11.1279714029905</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08408083995840586</v>
+        <v>0.08399590919533337</v>
       </c>
       <c r="C79">
-        <v>0.5081564341505105</v>
+        <v>0.4905143656559887</v>
       </c>
       <c r="D79">
-        <v>1.892056434150511</v>
+        <v>1.893114365655989</v>
       </c>
       <c r="E79">
-        <v>1.4399</v>
+        <v>1.4586</v>
       </c>
       <c r="F79">
-        <v>1.4399</v>
+        <v>1.4586</v>
       </c>
       <c r="G79">
         <v>0.056</v>
@@ -7765,28 +7765,28 @@
         <v>0.83</v>
       </c>
       <c r="M79">
-        <v>0.07458682000000001</v>
+        <v>0.07555548000000001</v>
       </c>
       <c r="N79">
-        <v>0.7554131799999999</v>
+        <v>0.75444452</v>
       </c>
       <c r="O79">
-        <v>0.113311977</v>
+        <v>0.113166678</v>
       </c>
       <c r="P79">
-        <v>0.642101203</v>
+        <v>0.6412778419999999</v>
       </c>
       <c r="Q79">
-        <v>0.9321012030000001</v>
+        <v>0.9312778420000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2181640867756777</v>
+        <v>0.2256932236151517</v>
       </c>
       <c r="T79">
-        <v>2.372656533168322</v>
+        <v>2.476297935768305</v>
       </c>
       <c r="U79">
         <v>0.0518</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>11.1279714029905</v>
+        <v>10.98530510295216</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08399590919533337</v>
+        <v>0.08391097843226089</v>
       </c>
       <c r="C80">
-        <v>0.4905143656559887</v>
+        <v>0.4728734808948956</v>
       </c>
       <c r="D80">
-        <v>1.893114365655989</v>
+        <v>1.894173480894896</v>
       </c>
       <c r="E80">
-        <v>1.4586</v>
+        <v>1.4773</v>
       </c>
       <c r="F80">
-        <v>1.4586</v>
+        <v>1.4773</v>
       </c>
       <c r="G80">
         <v>0.056</v>
@@ -7847,28 +7847,28 @@
         <v>0.83</v>
       </c>
       <c r="M80">
-        <v>0.07555548000000001</v>
+        <v>0.07652414</v>
       </c>
       <c r="N80">
-        <v>0.75444452</v>
+        <v>0.75347586</v>
       </c>
       <c r="O80">
-        <v>0.113166678</v>
+        <v>0.113021379</v>
       </c>
       <c r="P80">
-        <v>0.6412778419999999</v>
+        <v>0.640454481</v>
       </c>
       <c r="Q80">
-        <v>0.9312778420000001</v>
+        <v>0.9304544810000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2256932236151517</v>
+        <v>0.2339394211060043</v>
       </c>
       <c r="T80">
-        <v>2.476297935768305</v>
+        <v>2.589809948139715</v>
       </c>
       <c r="U80">
         <v>0.0518</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>10.98530510295216</v>
+        <v>10.84625060797808</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08391097843226089</v>
+        <v>0.08382604766918841</v>
       </c>
       <c r="C81">
-        <v>0.4728734808948956</v>
+        <v>0.4552337818550847</v>
       </c>
       <c r="D81">
-        <v>1.894173480894896</v>
+        <v>1.895233781855085</v>
       </c>
       <c r="E81">
-        <v>1.4773</v>
+        <v>1.496</v>
       </c>
       <c r="F81">
-        <v>1.4773</v>
+        <v>1.496</v>
       </c>
       <c r="G81">
         <v>0.056</v>
@@ -7929,28 +7929,28 @@
         <v>0.83</v>
       </c>
       <c r="M81">
-        <v>0.07652414</v>
+        <v>0.07749280000000001</v>
       </c>
       <c r="N81">
-        <v>0.75347586</v>
+        <v>0.7525071999999999</v>
       </c>
       <c r="O81">
-        <v>0.113021379</v>
+        <v>0.11287608</v>
       </c>
       <c r="P81">
-        <v>0.640454481</v>
+        <v>0.63963112</v>
       </c>
       <c r="Q81">
-        <v>0.9304544810000002</v>
+        <v>0.9296311200000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2339394211060043</v>
+        <v>0.2430102383459421</v>
       </c>
       <c r="T81">
-        <v>2.589809948139715</v>
+        <v>2.714673161748266</v>
       </c>
       <c r="U81">
         <v>0.0518</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>10.84625060797808</v>
+        <v>10.71067247537835</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08382604766918841</v>
+        <v>0.08374111690611594</v>
       </c>
       <c r="C82">
-        <v>0.4552337818550847</v>
+        <v>0.437595270528865</v>
       </c>
       <c r="D82">
-        <v>1.895233781855085</v>
+        <v>1.896295270528865</v>
       </c>
       <c r="E82">
-        <v>1.496</v>
+        <v>1.5147</v>
       </c>
       <c r="F82">
-        <v>1.496</v>
+        <v>1.5147</v>
       </c>
       <c r="G82">
         <v>0.056</v>
@@ -8011,28 +8011,28 @@
         <v>0.83</v>
       </c>
       <c r="M82">
-        <v>0.07749280000000001</v>
+        <v>0.07846146000000001</v>
       </c>
       <c r="N82">
-        <v>0.7525071999999999</v>
+        <v>0.75153854</v>
       </c>
       <c r="O82">
-        <v>0.11287608</v>
+        <v>0.112730781</v>
       </c>
       <c r="P82">
-        <v>0.63963112</v>
+        <v>0.638807759</v>
       </c>
       <c r="Q82">
-        <v>0.9296311200000001</v>
+        <v>0.9288077590000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2430102383459421</v>
+        <v>0.2530358784532418</v>
       </c>
       <c r="T82">
-        <v>2.714673161748266</v>
+        <v>2.852679871526139</v>
       </c>
       <c r="U82">
         <v>0.0518</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>10.71067247537835</v>
+        <v>10.57844195099097</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08374111690611594</v>
+        <v>0.08365618614304346</v>
       </c>
       <c r="C83">
-        <v>0.437595270528865</v>
+        <v>0.4199579489130094</v>
       </c>
       <c r="D83">
-        <v>1.896295270528865</v>
+        <v>1.897357948913009</v>
       </c>
       <c r="E83">
-        <v>1.5147</v>
+        <v>1.5334</v>
       </c>
       <c r="F83">
-        <v>1.5147</v>
+        <v>1.5334</v>
       </c>
       <c r="G83">
         <v>0.056</v>
@@ -8093,28 +8093,28 @@
         <v>0.83</v>
       </c>
       <c r="M83">
-        <v>0.07846146000000001</v>
+        <v>0.07943012000000001</v>
       </c>
       <c r="N83">
-        <v>0.75153854</v>
+        <v>0.7505698799999999</v>
       </c>
       <c r="O83">
-        <v>0.112730781</v>
+        <v>0.112585482</v>
       </c>
       <c r="P83">
-        <v>0.638807759</v>
+        <v>0.637984398</v>
       </c>
       <c r="Q83">
-        <v>0.9288077590000001</v>
+        <v>0.9279843980000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2530358784532418</v>
+        <v>0.2641754785724637</v>
       </c>
       <c r="T83">
-        <v>2.852679871526139</v>
+        <v>3.00602066016822</v>
       </c>
       <c r="U83">
         <v>0.0518</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>10.57844195099097</v>
+        <v>10.44943656134474</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08365618614304346</v>
+        <v>0.08357125537997098</v>
       </c>
       <c r="C84">
-        <v>0.4199579489130094</v>
+        <v>0.4023218190087705</v>
       </c>
       <c r="D84">
-        <v>1.897357948913009</v>
+        <v>1.898421819008771</v>
       </c>
       <c r="E84">
-        <v>1.5334</v>
+        <v>1.5521</v>
       </c>
       <c r="F84">
-        <v>1.5334</v>
+        <v>1.5521</v>
       </c>
       <c r="G84">
         <v>0.056</v>
@@ -8175,28 +8175,28 @@
         <v>0.83</v>
       </c>
       <c r="M84">
-        <v>0.07943012000000001</v>
+        <v>0.08039878000000002</v>
       </c>
       <c r="N84">
-        <v>0.7505698799999999</v>
+        <v>0.74960122</v>
       </c>
       <c r="O84">
-        <v>0.112585482</v>
+        <v>0.112440183</v>
       </c>
       <c r="P84">
-        <v>0.637984398</v>
+        <v>0.6371610369999999</v>
       </c>
       <c r="Q84">
-        <v>0.9279843980000001</v>
+        <v>0.9271610370000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2641754785724637</v>
+        <v>0.2766256198821823</v>
       </c>
       <c r="T84">
-        <v>3.00602066016822</v>
+        <v>3.177401541591722</v>
       </c>
       <c r="U84">
         <v>0.0518</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>10.44943656134474</v>
+        <v>10.32353973530444</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08357125537997098</v>
+        <v>0.08348632461689851</v>
       </c>
       <c r="C85">
-        <v>0.4023218190087705</v>
+        <v>0.3846868828218915</v>
       </c>
       <c r="D85">
-        <v>1.898421819008771</v>
+        <v>1.899486882821892</v>
       </c>
       <c r="E85">
-        <v>1.5521</v>
+        <v>1.5708</v>
       </c>
       <c r="F85">
-        <v>1.5521</v>
+        <v>1.5708</v>
       </c>
       <c r="G85">
         <v>0.056</v>
@@ -8257,28 +8257,28 @@
         <v>0.83</v>
       </c>
       <c r="M85">
-        <v>0.08039878000000002</v>
+        <v>0.08136744000000001</v>
       </c>
       <c r="N85">
-        <v>0.74960122</v>
+        <v>0.7486325599999999</v>
       </c>
       <c r="O85">
-        <v>0.112440183</v>
+        <v>0.112294884</v>
       </c>
       <c r="P85">
-        <v>0.6371610369999999</v>
+        <v>0.6363376759999999</v>
       </c>
       <c r="Q85">
-        <v>0.9271610370000001</v>
+        <v>0.9263376760000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2766256198821823</v>
+        <v>0.2906320288556157</v>
       </c>
       <c r="T85">
-        <v>3.177401541591722</v>
+        <v>3.370205033193162</v>
       </c>
       <c r="U85">
         <v>0.0518</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>10.32353973530444</v>
+        <v>10.20064045274129</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08348632461689851</v>
+        <v>0.08340139385382603</v>
       </c>
       <c r="C86">
-        <v>0.3846868828218917</v>
+        <v>0.3670531423626193</v>
       </c>
       <c r="D86">
-        <v>1.899486882821892</v>
+        <v>1.900553142362619</v>
       </c>
       <c r="E86">
-        <v>1.5708</v>
+        <v>1.5895</v>
       </c>
       <c r="F86">
-        <v>1.5708</v>
+        <v>1.5895</v>
       </c>
       <c r="G86">
         <v>0.056</v>
@@ -8339,28 +8339,28 @@
         <v>0.83</v>
       </c>
       <c r="M86">
-        <v>0.08136744</v>
+        <v>0.08233610000000001</v>
       </c>
       <c r="N86">
-        <v>0.74863256</v>
+        <v>0.7476638999999999</v>
       </c>
       <c r="O86">
-        <v>0.112294884</v>
+        <v>0.112149585</v>
       </c>
       <c r="P86">
-        <v>0.636337676</v>
+        <v>0.635514315</v>
       </c>
       <c r="Q86">
-        <v>0.9263376760000002</v>
+        <v>0.9255143150000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2906320288556156</v>
+        <v>0.3065059590255068</v>
       </c>
       <c r="T86">
-        <v>3.37020503319316</v>
+        <v>3.588715657008124</v>
       </c>
       <c r="U86">
         <v>0.0518</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>10.20064045274129</v>
+        <v>10.08063291800316</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08340139385382603</v>
+        <v>0.08331646309075352</v>
       </c>
       <c r="C87">
-        <v>0.3670531423626193</v>
+        <v>0.3494205996457174</v>
       </c>
       <c r="D87">
-        <v>1.900553142362619</v>
+        <v>1.901620599645717</v>
       </c>
       <c r="E87">
-        <v>1.5895</v>
+        <v>1.6082</v>
       </c>
       <c r="F87">
-        <v>1.5895</v>
+        <v>1.6082</v>
       </c>
       <c r="G87">
         <v>0.056</v>
@@ -8421,28 +8421,28 @@
         <v>0.83</v>
       </c>
       <c r="M87">
-        <v>0.08233610000000001</v>
+        <v>0.08330476000000001</v>
       </c>
       <c r="N87">
-        <v>0.7476638999999999</v>
+        <v>0.74669524</v>
       </c>
       <c r="O87">
-        <v>0.112149585</v>
+        <v>0.112004286</v>
       </c>
       <c r="P87">
-        <v>0.635514315</v>
+        <v>0.634690954</v>
       </c>
       <c r="Q87">
-        <v>0.9255143150000001</v>
+        <v>0.9246909540000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3065059590255068</v>
+        <v>0.3246475935053824</v>
       </c>
       <c r="T87">
-        <v>3.588715657008124</v>
+        <v>3.838442084225226</v>
       </c>
       <c r="U87">
         <v>0.0518</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>10.08063291800316</v>
+        <v>9.963416256165914</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08331646309075352</v>
+        <v>0.08323153232768105</v>
       </c>
       <c r="C88">
-        <v>0.3494205996457174</v>
+        <v>0.3317892566904768</v>
       </c>
       <c r="D88">
-        <v>1.901620599645717</v>
+        <v>1.902689256690477</v>
       </c>
       <c r="E88">
-        <v>1.6082</v>
+        <v>1.6269</v>
       </c>
       <c r="F88">
-        <v>1.6082</v>
+        <v>1.6269</v>
       </c>
       <c r="G88">
         <v>0.056</v>
@@ -8503,28 +8503,28 @@
         <v>0.83</v>
       </c>
       <c r="M88">
-        <v>0.08330476000000001</v>
+        <v>0.08427342</v>
       </c>
       <c r="N88">
-        <v>0.74669524</v>
+        <v>0.7457265799999999</v>
       </c>
       <c r="O88">
-        <v>0.112004286</v>
+        <v>0.111858987</v>
       </c>
       <c r="P88">
-        <v>0.634690954</v>
+        <v>0.633867593</v>
       </c>
       <c r="Q88">
-        <v>0.9246909540000001</v>
+        <v>0.9238675930000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3246475935053824</v>
+        <v>0.3455802486744696</v>
       </c>
       <c r="T88">
-        <v>3.838442084225226</v>
+        <v>4.126587961783422</v>
       </c>
       <c r="U88">
         <v>0.0518</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>9.963416256165914</v>
+        <v>9.848894230232972</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08323153232768105</v>
+        <v>0.08441820156460858</v>
       </c>
       <c r="C89">
-        <v>0.3317892566904768</v>
+        <v>0.2982657740004135</v>
       </c>
       <c r="D89">
-        <v>1.902689256690477</v>
+        <v>1.887865774000414</v>
       </c>
       <c r="E89">
-        <v>1.6269</v>
+        <v>1.6456</v>
       </c>
       <c r="F89">
-        <v>1.6269</v>
+        <v>1.6456</v>
       </c>
       <c r="G89">
         <v>0.056</v>
@@ -8585,45 +8585,45 @@
         <v>0.83</v>
       </c>
       <c r="M89">
-        <v>0.08427342</v>
+        <v>0.08803960000000001</v>
       </c>
       <c r="N89">
-        <v>0.7457265799999999</v>
+        <v>0.7419604</v>
       </c>
       <c r="O89">
-        <v>0.111858987</v>
+        <v>0.11129406</v>
       </c>
       <c r="P89">
-        <v>0.633867593</v>
+        <v>0.63066634</v>
       </c>
       <c r="Q89">
-        <v>0.9238675930000001</v>
+        <v>0.9206663400000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3455802486744696</v>
+        <v>0.3700016797050715</v>
       </c>
       <c r="T89">
-        <v>4.126587961783422</v>
+        <v>4.462758152267983</v>
       </c>
       <c r="U89">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V89">
         <v>0.15</v>
       </c>
       <c r="W89">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y89">
-        <v>9.848894230232972</v>
+        <v>9.427575772720456</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08441820156460858</v>
+        <v>0.08434772080153607</v>
       </c>
       <c r="C90">
-        <v>0.2982657740004135</v>
+        <v>0.2804397417694777</v>
       </c>
       <c r="D90">
-        <v>1.887865774000414</v>
+        <v>1.888739741769478</v>
       </c>
       <c r="E90">
-        <v>1.6456</v>
+        <v>1.6643</v>
       </c>
       <c r="F90">
-        <v>1.6456</v>
+        <v>1.6643</v>
       </c>
       <c r="G90">
         <v>0.056</v>
@@ -8667,28 +8667,28 @@
         <v>0.83</v>
       </c>
       <c r="M90">
-        <v>0.08803960000000001</v>
+        <v>0.08904005000000001</v>
       </c>
       <c r="N90">
-        <v>0.7419604</v>
+        <v>0.7409599499999999</v>
       </c>
       <c r="O90">
-        <v>0.11129406</v>
+        <v>0.1111439925</v>
       </c>
       <c r="P90">
-        <v>0.63066634</v>
+        <v>0.6298159575</v>
       </c>
       <c r="Q90">
-        <v>0.9206663400000001</v>
+        <v>0.9198159575000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3700016797050715</v>
+        <v>0.3988633709230554</v>
       </c>
       <c r="T90">
-        <v>4.462758152267983</v>
+        <v>4.860050195567919</v>
       </c>
       <c r="U90">
         <v>0.0535</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>9.427575772720456</v>
+        <v>9.321647955049439</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08434772080153607</v>
+        <v>0.08427724003846361</v>
       </c>
       <c r="C91">
-        <v>0.2804397417694777</v>
+        <v>0.2626145191018454</v>
       </c>
       <c r="D91">
-        <v>1.888739741769478</v>
+        <v>1.889614519101845</v>
       </c>
       <c r="E91">
-        <v>1.6643</v>
+        <v>1.683</v>
       </c>
       <c r="F91">
-        <v>1.6643</v>
+        <v>1.683</v>
       </c>
       <c r="G91">
         <v>0.056</v>
@@ -8749,28 +8749,28 @@
         <v>0.83</v>
       </c>
       <c r="M91">
-        <v>0.08904005000000001</v>
+        <v>0.0900405</v>
       </c>
       <c r="N91">
-        <v>0.7409599499999999</v>
+        <v>0.7399595</v>
       </c>
       <c r="O91">
-        <v>0.1111439925</v>
+        <v>0.110993925</v>
       </c>
       <c r="P91">
-        <v>0.6298159575</v>
+        <v>0.6289655750000001</v>
       </c>
       <c r="Q91">
-        <v>0.9198159575000001</v>
+        <v>0.9189655750000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3988633709230554</v>
+        <v>0.4334974003846362</v>
       </c>
       <c r="T91">
-        <v>4.860050195567919</v>
+        <v>5.336800647527842</v>
       </c>
       <c r="U91">
         <v>0.0535</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>9.321647955049439</v>
+        <v>9.218074088882226</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08427724003846361</v>
+        <v>0.08420675927539112</v>
       </c>
       <c r="C92">
-        <v>0.2626145191018454</v>
+        <v>0.2447901071228973</v>
       </c>
       <c r="D92">
-        <v>1.889614519101845</v>
+        <v>1.890490107122897</v>
       </c>
       <c r="E92">
-        <v>1.683</v>
+        <v>1.7017</v>
       </c>
       <c r="F92">
-        <v>1.683</v>
+        <v>1.7017</v>
       </c>
       <c r="G92">
         <v>0.056</v>
@@ -8831,28 +8831,28 @@
         <v>0.83</v>
       </c>
       <c r="M92">
-        <v>0.0900405</v>
+        <v>0.09104095000000001</v>
       </c>
       <c r="N92">
-        <v>0.7399595</v>
+        <v>0.73895905</v>
       </c>
       <c r="O92">
-        <v>0.110993925</v>
+        <v>0.1108438575</v>
       </c>
       <c r="P92">
-        <v>0.6289655750000001</v>
+        <v>0.6281151924999999</v>
       </c>
       <c r="Q92">
-        <v>0.9189655750000002</v>
+        <v>0.9181151925000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4334974003846362</v>
+        <v>0.4758278808376794</v>
       </c>
       <c r="T92">
-        <v>5.336800647527842</v>
+        <v>5.919495644367748</v>
       </c>
       <c r="U92">
         <v>0.0535</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>9.218074088882226</v>
+        <v>9.11677657142198</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08420675927539112</v>
+        <v>0.08413627851231864</v>
       </c>
       <c r="C93">
-        <v>0.2447901071228973</v>
+        <v>0.2269665069600979</v>
       </c>
       <c r="D93">
-        <v>1.890490107122897</v>
+        <v>1.891366506960098</v>
       </c>
       <c r="E93">
-        <v>1.7017</v>
+        <v>1.7204</v>
       </c>
       <c r="F93">
-        <v>1.7017</v>
+        <v>1.7204</v>
       </c>
       <c r="G93">
         <v>0.056</v>
@@ -8913,28 +8913,28 @@
         <v>0.83</v>
       </c>
       <c r="M93">
-        <v>0.09104095000000001</v>
+        <v>0.09204140000000001</v>
       </c>
       <c r="N93">
-        <v>0.73895905</v>
+        <v>0.7379585999999999</v>
       </c>
       <c r="O93">
-        <v>0.1108438575</v>
+        <v>0.11069379</v>
       </c>
       <c r="P93">
-        <v>0.6281151924999999</v>
+        <v>0.6272648099999999</v>
       </c>
       <c r="Q93">
-        <v>0.9181151925000001</v>
+        <v>0.91726481</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4758278808376794</v>
+        <v>0.5287409814039834</v>
       </c>
       <c r="T93">
-        <v>5.919495644367748</v>
+        <v>6.647864390417633</v>
       </c>
       <c r="U93">
         <v>0.0535</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>9.11677657142198</v>
+        <v>9.017681173906523</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08413627851231864</v>
+        <v>0.08406579774924616</v>
       </c>
       <c r="C94">
-        <v>0.2269665069600979</v>
+        <v>0.2091437197430044</v>
       </c>
       <c r="D94">
-        <v>1.891366506960098</v>
+        <v>1.892243719743004</v>
       </c>
       <c r="E94">
-        <v>1.7204</v>
+        <v>1.7391</v>
       </c>
       <c r="F94">
-        <v>1.7204</v>
+        <v>1.7391</v>
       </c>
       <c r="G94">
         <v>0.056</v>
@@ -8995,28 +8995,28 @@
         <v>0.83</v>
       </c>
       <c r="M94">
-        <v>0.09204140000000001</v>
+        <v>0.09304185000000001</v>
       </c>
       <c r="N94">
-        <v>0.7379585999999999</v>
+        <v>0.73695815</v>
       </c>
       <c r="O94">
-        <v>0.11069379</v>
+        <v>0.1105437225</v>
       </c>
       <c r="P94">
-        <v>0.6272648099999999</v>
+        <v>0.6264144275</v>
       </c>
       <c r="Q94">
-        <v>0.91726481</v>
+        <v>0.9164144275000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5287409814039834</v>
+        <v>0.5967721107035171</v>
       </c>
       <c r="T94">
-        <v>6.647864390417633</v>
+        <v>7.584338492481768</v>
       </c>
       <c r="U94">
         <v>0.0535</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>9.017681173906523</v>
+        <v>8.920716860208604</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08406579774924616</v>
+        <v>0.08399531698617368</v>
       </c>
       <c r="C95">
-        <v>0.2091437197430044</v>
+        <v>0.1913217466032702</v>
       </c>
       <c r="D95">
-        <v>1.892243719743004</v>
+        <v>1.89312174660327</v>
       </c>
       <c r="E95">
-        <v>1.7391</v>
+        <v>1.7578</v>
       </c>
       <c r="F95">
-        <v>1.7391</v>
+        <v>1.7578</v>
       </c>
       <c r="G95">
         <v>0.056</v>
@@ -9077,28 +9077,28 @@
         <v>0.83</v>
       </c>
       <c r="M95">
-        <v>0.09304185000000001</v>
+        <v>0.09404230000000001</v>
       </c>
       <c r="N95">
-        <v>0.73695815</v>
+        <v>0.7359576999999999</v>
       </c>
       <c r="O95">
-        <v>0.1105437225</v>
+        <v>0.110393655</v>
       </c>
       <c r="P95">
-        <v>0.6264144275</v>
+        <v>0.625564045</v>
       </c>
       <c r="Q95">
-        <v>0.9164144275000001</v>
+        <v>0.9155640450000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5967721107035171</v>
+        <v>0.6874802831028954</v>
       </c>
       <c r="T95">
-        <v>7.584338492481768</v>
+        <v>8.832970628567283</v>
       </c>
       <c r="U95">
         <v>0.0535</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>8.920716860208604</v>
+        <v>8.825815617014895</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08399531698617368</v>
+        <v>0.08392483622310121</v>
       </c>
       <c r="C96">
-        <v>0.1913217466032702</v>
+        <v>0.173500588674651</v>
       </c>
       <c r="D96">
-        <v>1.89312174660327</v>
+        <v>1.894000588674651</v>
       </c>
       <c r="E96">
-        <v>1.7578</v>
+        <v>1.7765</v>
       </c>
       <c r="F96">
-        <v>1.7578</v>
+        <v>1.7765</v>
       </c>
       <c r="G96">
         <v>0.056</v>
@@ -9159,28 +9159,28 @@
         <v>0.83</v>
       </c>
       <c r="M96">
-        <v>0.09404230000000001</v>
+        <v>0.09504275000000001</v>
       </c>
       <c r="N96">
-        <v>0.7359576999999999</v>
+        <v>0.7349572499999999</v>
       </c>
       <c r="O96">
-        <v>0.110393655</v>
+        <v>0.1102435875</v>
       </c>
       <c r="P96">
-        <v>0.625564045</v>
+        <v>0.6247136624999999</v>
       </c>
       <c r="Q96">
-        <v>0.9155640450000001</v>
+        <v>0.9147136625000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6874802831028954</v>
+        <v>0.8144717244620253</v>
       </c>
       <c r="T96">
-        <v>8.832970628567283</v>
+        <v>10.58105561908701</v>
       </c>
       <c r="U96">
         <v>0.0535</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>8.825815617014895</v>
+        <v>8.732912294730527</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08392483622310121</v>
+        <v>0.08385435546002873</v>
       </c>
       <c r="C97">
-        <v>0.173500588674651</v>
+        <v>0.1556802470930074</v>
       </c>
       <c r="D97">
-        <v>1.894000588674651</v>
+        <v>1.894880247093008</v>
       </c>
       <c r="E97">
-        <v>1.7765</v>
+        <v>1.7952</v>
       </c>
       <c r="F97">
-        <v>1.7765</v>
+        <v>1.7952</v>
       </c>
       <c r="G97">
         <v>0.056</v>
@@ -9241,28 +9241,28 @@
         <v>0.83</v>
       </c>
       <c r="M97">
-        <v>0.09504275000000001</v>
+        <v>0.09604320000000002</v>
       </c>
       <c r="N97">
-        <v>0.7349572499999999</v>
+        <v>0.7339568</v>
       </c>
       <c r="O97">
-        <v>0.1102435875</v>
+        <v>0.11009352</v>
       </c>
       <c r="P97">
-        <v>0.6247136624999999</v>
+        <v>0.62386328</v>
       </c>
       <c r="Q97">
-        <v>0.9147136625000001</v>
+        <v>0.9138632800000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8144717244620253</v>
+        <v>1.00495888650072</v>
       </c>
       <c r="T97">
-        <v>10.58105561908701</v>
+        <v>13.20318310486659</v>
       </c>
       <c r="U97">
         <v>0.0535</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>8.732912294730527</v>
+        <v>8.641944458327085</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08385435546002873</v>
+        <v>0.08378387469695625</v>
       </c>
       <c r="C98">
-        <v>0.1556802470930077</v>
+        <v>0.1378607229963129</v>
       </c>
       <c r="D98">
-        <v>1.894880247093008</v>
+        <v>1.895760722996313</v>
       </c>
       <c r="E98">
-        <v>1.7952</v>
+        <v>1.8139</v>
       </c>
       <c r="F98">
-        <v>1.7952</v>
+        <v>1.8139</v>
       </c>
       <c r="G98">
         <v>0.056</v>
@@ -9323,28 +9323,28 @@
         <v>0.83</v>
       </c>
       <c r="M98">
-        <v>0.09604320000000001</v>
+        <v>0.09704365</v>
       </c>
       <c r="N98">
-        <v>0.7339568</v>
+        <v>0.7329563499999999</v>
       </c>
       <c r="O98">
-        <v>0.11009352</v>
+        <v>0.1099434525</v>
       </c>
       <c r="P98">
-        <v>0.62386328</v>
+        <v>0.6230128975</v>
       </c>
       <c r="Q98">
-        <v>0.9138632800000002</v>
+        <v>0.9130128975000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.004958886500718</v>
+        <v>1.322437489898541</v>
       </c>
       <c r="T98">
-        <v>13.20318310486656</v>
+        <v>17.57339558116584</v>
       </c>
       <c r="U98">
         <v>0.0535</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>8.641944458327085</v>
+        <v>8.552852247416498</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08378387469695625</v>
+        <v>0.08371339393388377</v>
       </c>
       <c r="C99">
-        <v>0.1378607229963129</v>
+        <v>0.120042017524655</v>
       </c>
       <c r="D99">
-        <v>1.895760722996313</v>
+        <v>1.896642017524655</v>
       </c>
       <c r="E99">
-        <v>1.8139</v>
+        <v>1.8326</v>
       </c>
       <c r="F99">
-        <v>1.8139</v>
+        <v>1.8326</v>
       </c>
       <c r="G99">
         <v>0.056</v>
@@ -9405,28 +9405,28 @@
         <v>0.83</v>
       </c>
       <c r="M99">
-        <v>0.09704365</v>
+        <v>0.0980441</v>
       </c>
       <c r="N99">
-        <v>0.7329563499999999</v>
+        <v>0.7319559</v>
       </c>
       <c r="O99">
-        <v>0.1099434525</v>
+        <v>0.109793385</v>
       </c>
       <c r="P99">
-        <v>0.6230128975</v>
+        <v>0.622162515</v>
       </c>
       <c r="Q99">
-        <v>0.9130128975000001</v>
+        <v>0.9121625150000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.322437489898541</v>
+        <v>1.957394696694187</v>
       </c>
       <c r="T99">
-        <v>17.57339558116584</v>
+        <v>26.31382053376442</v>
       </c>
       <c r="U99">
         <v>0.0535</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>8.552852247416498</v>
+        <v>8.465578244891841</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08371339393388377</v>
+        <v>0.08364291317081128</v>
       </c>
       <c r="C100">
-        <v>0.120042017524655</v>
+        <v>0.102224131820243</v>
       </c>
       <c r="D100">
-        <v>1.896642017524655</v>
+        <v>1.897524131820243</v>
       </c>
       <c r="E100">
-        <v>1.8326</v>
+        <v>1.8513</v>
       </c>
       <c r="F100">
-        <v>1.8326</v>
+        <v>1.8513</v>
       </c>
       <c r="G100">
         <v>0.056</v>
@@ -9487,28 +9487,28 @@
         <v>0.83</v>
       </c>
       <c r="M100">
-        <v>0.0980441</v>
+        <v>0.09904455000000001</v>
       </c>
       <c r="N100">
-        <v>0.7319559</v>
+        <v>0.73095545</v>
       </c>
       <c r="O100">
-        <v>0.109793385</v>
+        <v>0.1096433175</v>
       </c>
       <c r="P100">
-        <v>0.622162515</v>
+        <v>0.6213121324999999</v>
       </c>
       <c r="Q100">
-        <v>0.9121625150000001</v>
+        <v>0.9113121325000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.957394696694187</v>
+        <v>3.862266317081126</v>
       </c>
       <c r="T100">
-        <v>26.31382053376442</v>
+        <v>52.53509539156015</v>
       </c>
       <c r="U100">
         <v>0.0535</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>8.465578244891841</v>
+        <v>8.380067353529295</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08364291317081128</v>
-      </c>
-      <c r="C101">
-        <v>0.102224131820243</v>
-      </c>
-      <c r="D101">
-        <v>1.897524131820243</v>
-      </c>
-      <c r="E101">
-        <v>1.8513</v>
-      </c>
-      <c r="F101">
-        <v>1.8513</v>
-      </c>
-      <c r="G101">
-        <v>0.056</v>
-      </c>
-      <c r="H101">
-        <v>1.87</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.12</v>
-      </c>
-      <c r="K101">
-        <v>0.2900000000000001</v>
-      </c>
-      <c r="L101">
-        <v>0.83</v>
-      </c>
-      <c r="M101">
-        <v>0.09904455000000001</v>
-      </c>
-      <c r="N101">
-        <v>0.73095545</v>
-      </c>
-      <c r="O101">
-        <v>0.1096433175</v>
-      </c>
-      <c r="P101">
-        <v>0.6213121324999999</v>
-      </c>
-      <c r="Q101">
-        <v>0.9113121325000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.862266317081126</v>
-      </c>
-      <c r="T101">
-        <v>52.53509539156015</v>
-      </c>
-      <c r="U101">
-        <v>0.0535</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.04547499999999999</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A1/A+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>8.380067353529295</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
